--- a/AAII_Financials/Quarterly/PBFS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PBFS_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>PBFS</t>
   </si>
@@ -656,185 +656,191 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E8" s="3">
         <v>20200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>19100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>18800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>18000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>15200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>28400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>14600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>13600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>13300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>13000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -904,8 +910,11 @@
       <c r="Y9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -975,8 +984,11 @@
       <c r="Y10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,8 +1014,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1073,8 +1086,11 @@
       <c r="Y12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,8 +1160,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1215,8 +1234,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1271,8 +1293,8 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>5</v>
+      <c r="U15" s="3">
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>5</v>
@@ -1286,8 +1308,11 @@
       <c r="Y15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E17" s="3">
         <v>5000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>-400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4700</v>
-      </c>
-      <c r="T17" s="3">
-        <v>1900</v>
       </c>
       <c r="U17" s="3">
         <v>1900</v>
       </c>
       <c r="V17" s="3">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="W17" s="3">
         <v>1700</v>
       </c>
       <c r="X17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Y17" s="3">
         <v>1600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E18" s="3">
         <v>15200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>16000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>17500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>17600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>14600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>12500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>8800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>23700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>12700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>12300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>11900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>11600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>11400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,150 +1511,157 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-10900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-10200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-9900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-9600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-8100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-9500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-12900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-7600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-7100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-8500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-20400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-14300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-6100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E21" s="3">
         <v>5000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3200</v>
-      </c>
-      <c r="P21" s="3">
-        <v>2400</v>
       </c>
       <c r="Q21" s="3">
         <v>2400</v>
       </c>
       <c r="R21" s="3">
+        <v>2400</v>
+      </c>
+      <c r="S21" s="3">
         <v>1800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>7200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>6900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>6200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1692,150 +1731,159 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2400</v>
-      </c>
-      <c r="P23" s="3">
-        <v>1700</v>
       </c>
       <c r="Q23" s="3">
         <v>1700</v>
       </c>
       <c r="R23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="S23" s="3">
         <v>1100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>800</v>
+      </c>
+      <c r="E24" s="3">
         <v>900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1800</v>
-      </c>
-      <c r="L24" s="3">
-        <v>400</v>
       </c>
       <c r="M24" s="3">
         <v>400</v>
       </c>
       <c r="N24" s="3">
+        <v>400</v>
+      </c>
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>300</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>200</v>
       </c>
       <c r="R24" s="3">
         <v>200</v>
       </c>
       <c r="S24" s="3">
+        <v>200</v>
+      </c>
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E26" s="3">
         <v>3400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5000</v>
-      </c>
-      <c r="V26" s="3">
-        <v>4800</v>
       </c>
       <c r="W26" s="3">
         <v>4800</v>
       </c>
       <c r="X26" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Y26" s="3">
         <v>4400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E27" s="3">
         <v>3400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5000</v>
-      </c>
-      <c r="V27" s="3">
-        <v>4800</v>
       </c>
       <c r="W27" s="3">
         <v>4800</v>
       </c>
       <c r="X27" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Y27" s="3">
         <v>4400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2180,17 +2240,20 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,150 +2397,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E32" s="3">
         <v>10900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>10200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>9900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>9600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>8100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>9500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>12900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>7600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>7900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>7100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>8500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>20400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>14300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>6100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>5800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E33" s="3">
         <v>3400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5000</v>
-      </c>
-      <c r="V33" s="3">
-        <v>4800</v>
       </c>
       <c r="W33" s="3">
         <v>4800</v>
       </c>
       <c r="X33" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Y33" s="3">
         <v>4400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E35" s="3">
         <v>3400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5000</v>
-      </c>
-      <c r="V35" s="3">
-        <v>4800</v>
       </c>
       <c r="W35" s="3">
         <v>4800</v>
       </c>
       <c r="X35" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Y35" s="3">
         <v>4400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,150 +2830,157 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E41" s="3">
         <v>83800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>33600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>27300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>33500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>52600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>29800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>32800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>26300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>58400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>24500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>25500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>34500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>37400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>21200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>22900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>24600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>41600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>48400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>38300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>28000</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>108200</v>
+      </c>
+      <c r="E42" s="3">
         <v>134000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>118100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>118900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>114900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>351400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>347300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>433200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>323900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>421500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>301700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>304200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>162500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>225700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>136700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>209200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>106800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>167100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>182600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>119300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>30700</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2958,8 +3050,11 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3029,8 +3124,11 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3100,8 +3198,11 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3171,8 +3272,11 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3242,150 +3346,159 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E48" s="3">
         <v>41500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>41600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>42200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>42600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>43300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>37300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>37800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>38200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>38500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>38900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>39300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>39700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>40300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>40900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>41300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>41500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>41600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>41700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>41800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>42000</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E49" s="3">
         <v>14200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11200</v>
-      </c>
-      <c r="L49" s="3">
-        <v>9100</v>
       </c>
       <c r="M49" s="3">
         <v>9100</v>
       </c>
       <c r="N49" s="3">
+        <v>9100</v>
+      </c>
+      <c r="O49" s="3">
         <v>9200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9400</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>9500</v>
       </c>
       <c r="R49" s="3">
         <v>9500</v>
       </c>
       <c r="S49" s="3">
+        <v>9500</v>
+      </c>
+      <c r="T49" s="3">
         <v>9600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10000</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,8 +3642,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3597,8 +3716,11 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3790,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1852900</v>
+      </c>
+      <c r="E54" s="3">
         <v>1963400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1856200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1864300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1834500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2069600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1964200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1974100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1843200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1967700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1796300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1788500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1574200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1629000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1526400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1499700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1391800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1449900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1480000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1385500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1287000</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,8 +3922,9 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3834,15 +3964,15 @@
       <c r="O57" s="3">
         <v>0</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q57" s="3">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R57" s="3">
         <v>7800</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3855,8 +3985,8 @@
       <c r="V57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
+      <c r="W57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X57" s="3">
         <v>0</v>
@@ -3864,8 +3994,11 @@
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3935,26 +4068,29 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E59" s="3">
         <v>5800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5900</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>5</v>
       </c>
@@ -3970,8 +4106,8 @@
       <c r="M59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N59" s="3">
-        <v>0</v>
+      <c r="N59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O59" s="3">
         <v>0</v>
@@ -4006,8 +4142,11 @@
       <c r="Y59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4077,8 +4216,11 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4092,11 +4234,11 @@
         <v>700</v>
       </c>
       <c r="G61" s="3">
+        <v>700</v>
+      </c>
+      <c r="H61" s="3">
         <v>800</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -4148,8 +4290,11 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4219,8 +4364,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4586,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1569100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1691600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1589500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1604400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1584800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1827900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1721600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1737000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1599200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1728500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1558400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1559800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1346700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1403600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1302400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1271200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1163800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1226200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1345000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1253800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1160600</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +4984,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>180200</v>
+      </c>
+      <c r="E72" s="3">
         <v>177000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>173000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>168500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>162500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>156300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>151100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>148700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>148400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>142200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>140800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>144400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>143000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>141100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>139700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>139000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>138100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>134300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>135400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>130400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>125600</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5280,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>283800</v>
+      </c>
+      <c r="E76" s="3">
         <v>271800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>266700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>259900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>249700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>241700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>242600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>237100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>244000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>239100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>237800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>228700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>227400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>225400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>224000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>228500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>228000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>223800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>135000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>131800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>126400</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E81" s="3">
         <v>3400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5000</v>
-      </c>
-      <c r="V81" s="3">
-        <v>4800</v>
       </c>
       <c r="W81" s="3">
         <v>4800</v>
       </c>
       <c r="X81" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Y81" s="3">
         <v>4400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,13 +5611,14 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E83" s="3">
         <v>700</v>
@@ -5465,10 +5663,10 @@
         <v>700</v>
       </c>
       <c r="S83" s="3">
+        <v>700</v>
+      </c>
+      <c r="T83" s="3">
         <v>1500</v>
-      </c>
-      <c r="T83" s="3">
-        <v>700</v>
       </c>
       <c r="U83" s="3">
         <v>700</v>
@@ -5485,8 +5683,11 @@
       <c r="Y83" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6053,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
         <v>12400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13600</v>
-      </c>
-      <c r="F89" s="3">
-        <v>2300</v>
       </c>
       <c r="G89" s="3">
         <v>2300</v>
       </c>
       <c r="H89" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I89" s="3">
         <v>8000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>21400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>22800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>21500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-18400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>11000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>7200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,25 +6157,26 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
@@ -5965,34 +6185,34 @@
         <v>-100</v>
       </c>
       <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-500</v>
       </c>
       <c r="U91" s="3">
         <v>-500</v>
@@ -6001,16 +6221,19 @@
         <v>-500</v>
       </c>
       <c r="W91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X91" s="3">
         <v>-700</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-600</v>
       </c>
       <c r="Y91" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6377,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>37200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-39000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>11200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-29100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-20000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-77000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-81100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-38400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-99400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-17700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-57500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-12600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-39300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-16000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-14900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>2600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-62600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-10100</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6320,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,79 +6775,85 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-113100</v>
+      </c>
+      <c r="E100" s="3">
         <v>92600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-19400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>24500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-237900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>95800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-29000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>131200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-123100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>170000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>210500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-56300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>107600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>14800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>106300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-86900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-24400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>90000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>97600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-89400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>83500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-30300</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6675,75 +6923,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-76900</v>
+      </c>
+      <c r="E102" s="3">
         <v>66100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-255600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>26800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-88700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>115600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-129400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>153600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>132600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-66200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>105300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-33300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>75300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-115200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-41300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>73300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>100300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-92000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>28100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-37400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PBFS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PBFS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
   <si>
     <t>PBFS</t>
   </si>
@@ -656,191 +656,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E8" s="3">
         <v>21500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>19100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>18800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>18000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>15200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>12100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>13300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>28400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>14200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>13600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>13300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>13000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -913,8 +920,11 @@
       <c r="Z9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -987,8 +997,11 @@
       <c r="Z10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1015,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1089,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,8 +1180,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1237,8 +1257,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1296,8 +1319,8 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>5</v>
+      <c r="V15" s="3">
+        <v>0</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>5</v>
@@ -1311,8 +1334,11 @@
       <c r="Z15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E17" s="3">
         <v>6500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>-400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4700</v>
-      </c>
-      <c r="U17" s="3">
-        <v>1900</v>
       </c>
       <c r="V17" s="3">
         <v>1900</v>
       </c>
       <c r="W17" s="3">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="X17" s="3">
         <v>1700</v>
       </c>
       <c r="Y17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Z17" s="3">
         <v>1600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E18" s="3">
         <v>15000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>15200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>16000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>17500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>17600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>14600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>12500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>8800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>23700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>12700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>12300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>11900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>11600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,156 +1545,163 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-11000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-10900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-10200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-9900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-9600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-9400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-12900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-7600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-7900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-7100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-8500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-20400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-14300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-5700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E21" s="3">
         <v>4700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3200</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>2400</v>
       </c>
       <c r="R21" s="3">
         <v>2400</v>
       </c>
       <c r="S21" s="3">
+        <v>2400</v>
+      </c>
+      <c r="T21" s="3">
         <v>1800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>7200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>6900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>6300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1734,156 +1774,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E23" s="3">
         <v>4000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2400</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>1700</v>
       </c>
       <c r="R23" s="3">
         <v>1700</v>
       </c>
       <c r="S23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="T23" s="3">
         <v>1100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1800</v>
-      </c>
-      <c r="M24" s="3">
-        <v>400</v>
       </c>
       <c r="N24" s="3">
         <v>400</v>
       </c>
       <c r="O24" s="3">
+        <v>400</v>
+      </c>
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>300</v>
-      </c>
-      <c r="R24" s="3">
-        <v>200</v>
       </c>
       <c r="S24" s="3">
         <v>200</v>
       </c>
       <c r="T24" s="3">
+        <v>200</v>
+      </c>
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E26" s="3">
         <v>3200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5000</v>
-      </c>
-      <c r="W26" s="3">
-        <v>4800</v>
       </c>
       <c r="X26" s="3">
         <v>4800</v>
       </c>
       <c r="Y26" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Z26" s="3">
         <v>4400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E27" s="3">
         <v>3200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5000</v>
-      </c>
-      <c r="W27" s="3">
-        <v>4800</v>
       </c>
       <c r="X27" s="3">
         <v>4800</v>
       </c>
       <c r="Y27" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Z27" s="3">
         <v>4400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2243,17 +2304,20 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,156 +2467,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E32" s="3">
         <v>11000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>10900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>10200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>9900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>9600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>9400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>12900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>7600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>6600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>7900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>7100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>8500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>20400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>14300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>5700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>6100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>5800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E33" s="3">
         <v>3200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5000</v>
-      </c>
-      <c r="W33" s="3">
-        <v>4800</v>
       </c>
       <c r="X33" s="3">
         <v>4800</v>
       </c>
       <c r="Y33" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Z33" s="3">
         <v>4400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E35" s="3">
         <v>3200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5000</v>
-      </c>
-      <c r="W35" s="3">
-        <v>4800</v>
       </c>
       <c r="X35" s="3">
         <v>4800</v>
       </c>
       <c r="Y35" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Z35" s="3">
         <v>4400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,156 +2917,163 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E41" s="3">
         <v>32600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>83800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>33600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>27300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>52600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>29800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>32800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>26300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>58400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>25500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>34500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>37400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>21200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>22900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>24600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>41600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>48400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>38300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>28000</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>209400</v>
+      </c>
+      <c r="E42" s="3">
         <v>108200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>134000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>118100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>118900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>114900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>351400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>347300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>433200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>323900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>421500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>301700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>304200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>162500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>225700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>136700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>209200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>106800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>167100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>182600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>119300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>30700</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3053,8 +3146,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3127,8 +3223,11 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3201,8 +3300,11 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3275,8 +3377,11 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3349,156 +3454,165 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E48" s="3">
         <v>41100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>41500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>41600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>42200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>42600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>43300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>37300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>37800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>38200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>38500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>38900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>39300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>39700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>40300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>40900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>41300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>41500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>41600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>41700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>41800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>42000</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E49" s="3">
         <v>14100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11200</v>
-      </c>
-      <c r="M49" s="3">
-        <v>9100</v>
       </c>
       <c r="N49" s="3">
         <v>9100</v>
       </c>
       <c r="O49" s="3">
+        <v>9100</v>
+      </c>
+      <c r="P49" s="3">
         <v>9200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9400</v>
-      </c>
-      <c r="R49" s="3">
-        <v>9500</v>
       </c>
       <c r="S49" s="3">
         <v>9500</v>
       </c>
       <c r="T49" s="3">
+        <v>9500</v>
+      </c>
+      <c r="U49" s="3">
         <v>9600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10000</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,8 +3762,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3719,8 +3839,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1981800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1852900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1963400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1856200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1864300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1834500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2069600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1964200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1974100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1843200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1967700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1796300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1788500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1574200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1629000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1526400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1499700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1391800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1449900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1480000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1385500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1287000</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,8 +4053,9 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3967,15 +4098,15 @@
       <c r="P57" s="3">
         <v>0</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R57" s="3">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S57" s="3">
         <v>7800</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3988,8 +4119,8 @@
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
+      <c r="X57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y57" s="3">
         <v>0</v>
@@ -3997,8 +4128,11 @@
       <c r="Z57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4071,29 +4205,32 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E59" s="3">
         <v>5700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5900</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4109,8 +4246,8 @@
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
+      <c r="O59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -4145,8 +4282,11 @@
       <c r="Z59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4219,8 +4359,11 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4237,11 +4380,11 @@
         <v>700</v>
       </c>
       <c r="H61" s="3">
+        <v>700</v>
+      </c>
+      <c r="I61" s="3">
         <v>800</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -4293,8 +4436,11 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4367,8 +4513,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,82 +4744,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1692900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1569100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1691600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1589500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1604400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1584800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1827900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1721600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1737000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1599200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1728500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1558400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1559800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1346700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1403600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1302400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1271200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1163800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1226200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1345000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1253800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1160600</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,82 +5158,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>184900</v>
+      </c>
+      <c r="E72" s="3">
         <v>180200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>177000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>173000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>168500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>162500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>156300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>151100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>148700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>148400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>142200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>140800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>144400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>143000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>141100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>139700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>139000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>138100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>134300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>135400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>130400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>125600</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>289000</v>
+      </c>
+      <c r="E76" s="3">
         <v>283800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>271800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>266700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>259900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>249700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>241700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>242600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>237100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>244000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>239100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>237800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>228700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>227400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>225400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>224000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>228500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>228000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>223800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>135000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>131800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>126400</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E81" s="3">
         <v>3200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5000</v>
-      </c>
-      <c r="W81" s="3">
-        <v>4800</v>
       </c>
       <c r="X81" s="3">
         <v>4800</v>
       </c>
       <c r="Y81" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Z81" s="3">
         <v>4400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,8 +5810,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5621,7 +5820,7 @@
         <v>600</v>
       </c>
       <c r="E83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F83" s="3">
         <v>700</v>
@@ -5666,10 +5865,10 @@
         <v>700</v>
       </c>
       <c r="T83" s="3">
+        <v>700</v>
+      </c>
+      <c r="U83" s="3">
         <v>1500</v>
-      </c>
-      <c r="U83" s="3">
-        <v>700</v>
       </c>
       <c r="V83" s="3">
         <v>700</v>
@@ -5686,8 +5885,11 @@
       <c r="Z83" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>12400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13600</v>
-      </c>
-      <c r="G89" s="3">
-        <v>2300</v>
       </c>
       <c r="H89" s="3">
         <v>2400</v>
       </c>
       <c r="I89" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J89" s="3">
         <v>8000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>21400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>22800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>21500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-18400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>11000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>7200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,28 +6378,29 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
@@ -6188,34 +6409,34 @@
         <v>-100</v>
       </c>
       <c r="L91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-500</v>
       </c>
       <c r="V91" s="3">
         <v>-500</v>
@@ -6224,16 +6445,19 @@
         <v>-500</v>
       </c>
       <c r="X91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-700</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-600</v>
       </c>
       <c r="Z91" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,82 +6607,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="E94" s="3">
         <v>37200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-39000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>11200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-29100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-20000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-77000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-81100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-38400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-22300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-99400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-17700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-57500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-12600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-39300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-16000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-14900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>2600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-62600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-10100</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,82 +7021,88 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>124600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-113100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>92600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-19400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>24500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-237900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>95800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-29000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>131200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-123100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>170000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>210500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-56300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>107600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>14800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>106300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-86900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-24400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>90000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>97600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-89400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>83500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-30300</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6926,78 +7175,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>106900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-76900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>66100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-255600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>26800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-88700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>115600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-129400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>153600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>132600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-66200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>105300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-33300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>75300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-115200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-41300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>73300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>100300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-92000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>28100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-37400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PBFS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PBFS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
   <si>
     <t>PBFS</t>
   </si>
@@ -656,198 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>23100</v>
+        <v>22900</v>
       </c>
       <c r="E8" s="3">
+        <v>20100</v>
+      </c>
+      <c r="F8" s="3">
         <v>21500</v>
       </c>
-      <c r="F8" s="3">
-        <v>20200</v>
-      </c>
       <c r="G8" s="3">
+        <v>13900</v>
+      </c>
+      <c r="H8" s="3">
+        <v>18700</v>
+      </c>
+      <c r="I8" s="3">
         <v>19100</v>
       </c>
-      <c r="H8" s="3">
-        <v>18800</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
+        <v>20800</v>
+      </c>
+      <c r="K8" s="3">
         <v>18000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>15200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>12100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>10200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>10900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>10600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>10700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>10900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>11200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>11100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>10900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>13300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>28400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>14600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>14200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>13600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>13300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>13000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -923,31 +937,37 @@
       <c r="AA9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>20100</v>
+      </c>
+      <c r="F10" s="3">
+        <v>21500</v>
+      </c>
+      <c r="G10" s="3">
+        <v>13900</v>
+      </c>
+      <c r="H10" s="3">
+        <v>18700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>19100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>20800</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1000,8 +1020,14 @@
       <c r="AA10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,8 +1055,10 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1106,8 +1134,14 @@
       <c r="AA12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,31 +1217,37 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>-6000</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1260,31 +1300,37 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1322,11 +1368,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>5</v>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>5</v>
@@ -1337,8 +1383,14 @@
       <c r="AA15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1415,176 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5900</v>
+        <v>14400</v>
       </c>
       <c r="E17" s="3">
-        <v>6500</v>
+        <v>14800</v>
       </c>
       <c r="F17" s="3">
-        <v>5000</v>
+        <v>15200</v>
       </c>
       <c r="G17" s="3">
-        <v>3100</v>
+        <v>15500</v>
       </c>
       <c r="H17" s="3">
-        <v>1300</v>
+        <v>14100</v>
       </c>
       <c r="I17" s="3">
+        <v>13100</v>
+      </c>
+      <c r="J17" s="3">
+        <v>12900</v>
+      </c>
+      <c r="K17" s="3">
         <v>400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>-400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>4700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>17200</v>
+        <v>8500</v>
       </c>
       <c r="E18" s="3">
-        <v>15000</v>
+        <v>5300</v>
       </c>
       <c r="F18" s="3">
-        <v>15200</v>
+        <v>6300</v>
       </c>
       <c r="G18" s="3">
-        <v>16000</v>
+        <v>-1700</v>
       </c>
       <c r="H18" s="3">
-        <v>17500</v>
+        <v>4600</v>
       </c>
       <c r="I18" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>7900</v>
+      </c>
+      <c r="K18" s="3">
         <v>17600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>14600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>12500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>9900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>10500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>10000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>9800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>9200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>9100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>9600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>8800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>9500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>23700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>12700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>12300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>11900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>11600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>11400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,185 +1612,199 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-11200</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
-        <v>-11000</v>
+        <v>300</v>
       </c>
       <c r="F20" s="3">
-        <v>-10900</v>
+        <v>300</v>
       </c>
       <c r="G20" s="3">
-        <v>-10200</v>
+        <v>300</v>
       </c>
       <c r="H20" s="3">
-        <v>-9900</v>
+        <v>300</v>
       </c>
       <c r="I20" s="3">
+        <v>300</v>
+      </c>
+      <c r="J20" s="3">
+        <v>200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-9600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-8100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-9500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-9400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-2500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-8200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-12900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-6600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-7900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-7100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-8500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-20400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-14300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-5800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F21" s="3">
         <v>6700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>6400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>8300</v>
+      </c>
+      <c r="K21" s="3">
+        <v>8700</v>
+      </c>
+      <c r="L21" s="3">
+        <v>7200</v>
+      </c>
+      <c r="M21" s="3">
+        <v>3700</v>
+      </c>
+      <c r="N21" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O21" s="3">
+        <v>8700</v>
+      </c>
+      <c r="P21" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="R21" s="3">
+        <v>2300</v>
+      </c>
+      <c r="S21" s="3">
+        <v>3200</v>
+      </c>
+      <c r="T21" s="3">
+        <v>2400</v>
+      </c>
+      <c r="U21" s="3">
+        <v>2400</v>
+      </c>
+      <c r="V21" s="3">
+        <v>1800</v>
+      </c>
+      <c r="W21" s="3">
         <v>4700</v>
       </c>
-      <c r="F21" s="3">
-        <v>5000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>6400</v>
-      </c>
-      <c r="H21" s="3">
-        <v>8300</v>
-      </c>
-      <c r="I21" s="3">
-        <v>8700</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="X21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Y21" s="3">
         <v>7200</v>
       </c>
-      <c r="K21" s="3">
-        <v>3700</v>
-      </c>
-      <c r="L21" s="3">
-        <v>1100</v>
-      </c>
-      <c r="M21" s="3">
-        <v>8700</v>
-      </c>
-      <c r="N21" s="3">
-        <v>2400</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="P21" s="3">
-        <v>2300</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>3200</v>
-      </c>
-      <c r="R21" s="3">
-        <v>2400</v>
-      </c>
-      <c r="S21" s="3">
-        <v>2400</v>
-      </c>
-      <c r="T21" s="3">
-        <v>1800</v>
-      </c>
-      <c r="U21" s="3">
-        <v>4700</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-900</v>
-      </c>
-      <c r="W21" s="3">
-        <v>7200</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>6900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>6200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>6300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1777,162 +1857,180 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F23" s="3">
         <v>6100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>4000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>4300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>5700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>7700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>8000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>6500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>3100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>8100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-3100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>2400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>3300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-1600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>6500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>6200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>5500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>5700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F24" s="3">
         <v>1300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>1600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>1800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
-      </c>
-      <c r="P24" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>600</v>
       </c>
       <c r="R24" s="3">
         <v>300</v>
       </c>
       <c r="S24" s="3">
+        <v>600</v>
+      </c>
+      <c r="T24" s="3">
+        <v>300</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>1500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>1400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>1200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2106,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F26" s="3">
         <v>4700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>3200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>3400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>4500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>6000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>6200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>5200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>2400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>6300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>1400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-3600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>1900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>1400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>1500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>2900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>5000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>4800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>4800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>4400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F27" s="3">
         <v>4700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>3200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>3400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>4500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>6000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>6200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>5200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>2400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>6300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>1400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-3600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>1900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>1400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>1500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>2900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-1000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>5000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>4800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>4800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>4400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2355,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2307,17 +2429,23 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2521,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,162 +2604,180 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>11200</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
-        <v>11000</v>
+        <v>-300</v>
       </c>
       <c r="F32" s="3">
-        <v>10900</v>
+        <v>-300</v>
       </c>
       <c r="G32" s="3">
-        <v>10200</v>
+        <v>-300</v>
       </c>
       <c r="H32" s="3">
-        <v>9900</v>
+        <v>-300</v>
       </c>
       <c r="I32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K32" s="3">
         <v>9600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>8100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>9500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>9400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>2500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>8200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>12900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>7600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>6600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>7900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>7100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>8500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>20400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>14300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>5800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>5700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>6100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>5800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F33" s="3">
         <v>4700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>3200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>3400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>4500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>6000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>6200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>5200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>2400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>6300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>1400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-3600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>1900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>1500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>2900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>5000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>4800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>4800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>4400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2853,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F35" s="3">
         <v>4700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>3200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>3400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>4500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>6000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>6200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>5200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>2400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>6300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>1400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-3600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>1900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>1500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>2900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>5000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>4800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>4800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>4400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +3059,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,185 +3090,199 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>38500</v>
+        <v>225000</v>
       </c>
       <c r="E41" s="3">
-        <v>32600</v>
+        <v>165200</v>
       </c>
       <c r="F41" s="3">
-        <v>83800</v>
+        <v>246500</v>
       </c>
       <c r="G41" s="3">
-        <v>33600</v>
+        <v>139600</v>
       </c>
       <c r="H41" s="3">
-        <v>27300</v>
+        <v>216500</v>
       </c>
       <c r="I41" s="3">
+        <v>150500</v>
+      </c>
+      <c r="J41" s="3">
+        <v>145100</v>
+      </c>
+      <c r="K41" s="3">
         <v>33500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>52600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>29800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>32800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>26300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>58400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>24500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>25500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>34500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>37400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>21200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>22900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>24600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>41600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>48400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>38300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>28000</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>209400</v>
+        <v>400</v>
       </c>
       <c r="E42" s="3">
-        <v>108200</v>
+        <v>200</v>
       </c>
       <c r="F42" s="3">
-        <v>134000</v>
+        <v>100</v>
       </c>
       <c r="G42" s="3">
-        <v>118100</v>
+        <v>200</v>
       </c>
       <c r="H42" s="3">
-        <v>118900</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>700</v>
+      </c>
+      <c r="J42" s="3">
+        <v>200</v>
+      </c>
+      <c r="K42" s="3">
         <v>114900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>351400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>347300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>433200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>323900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>421500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>301700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>304200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>162500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>225700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>136700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>209200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>106800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>167100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>182600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>119300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>30700</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3149,31 +3335,37 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3226,31 +3418,37 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -3303,31 +3501,37 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>233000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>172900</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>254400</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>147500</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>223700</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>158400</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>158400</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -3380,31 +3584,37 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>290800</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>286000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>321600</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>348000</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>439900</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>459200</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>531500</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3457,162 +3667,180 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>40100</v>
+      </c>
+      <c r="F48" s="3">
         <v>40700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>41100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>41500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>41600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>42200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>42600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>43300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>37300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>37800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>38200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>38500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>38900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>39300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>39700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>40300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>40900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>41300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>41500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>41600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>41700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>41800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>42000</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>13800</v>
+      </c>
+      <c r="F49" s="3">
         <v>14000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>14100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>14200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>10900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>11000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>11100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>11200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>11300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>11400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>11200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>9100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>9100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>9200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>9300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>9400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>9500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>9500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>9600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>9700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>9800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>9900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>10000</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA49" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3916,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,31 +3999,37 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>37700</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>38200</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>39000</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>38500</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>40600</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>36700</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3842,8 +4082,14 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,85 +4165,97 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2014600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1895400</v>
+      </c>
+      <c r="F54" s="3">
         <v>1981800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1852900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1963400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1856200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1864300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1834500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2069600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1964200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1974100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1843200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1967700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1796300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1788500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1574200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1629000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1526400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1499700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1391800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1449900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1480000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1385500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1287000</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA54" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4283,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,31 +4314,33 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>1675300</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>1550300</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>1648000</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>1522100</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>1638800</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>1541900</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>1564600</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -4101,18 +4363,18 @@
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
+      <c r="R57" s="3">
+        <v>0</v>
       </c>
       <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U57" s="3">
         <v>7800</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4122,40 +4384,46 @@
       <c r="X57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>0</v>
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>9700</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>17500</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>34100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>23100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>18800</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>15400</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4208,35 +4476,41 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>5600</v>
-      </c>
-      <c r="E59" s="3">
-        <v>5700</v>
-      </c>
-      <c r="F59" s="3">
-        <v>5800</v>
-      </c>
-      <c r="G59" s="3">
-        <v>5700</v>
-      </c>
-      <c r="H59" s="3">
-        <v>5800</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
         <v>5900</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4249,11 +4523,11 @@
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>0</v>
+      <c r="P59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R59" s="3">
         <v>0</v>
@@ -4285,31 +4559,37 @@
       <c r="AA59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>1685000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>1567800</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>1666000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>1556200</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>1661900</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>1560700</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>1580000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -4362,35 +4642,41 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>700</v>
+        <v>5400</v>
       </c>
       <c r="F61" s="3">
-        <v>700</v>
+        <v>5500</v>
       </c>
       <c r="G61" s="3">
-        <v>700</v>
+        <v>5600</v>
       </c>
       <c r="H61" s="3">
-        <v>700</v>
+        <v>5700</v>
       </c>
       <c r="I61" s="3">
+        <v>6400</v>
+      </c>
+      <c r="J61" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K61" s="3">
         <v>800</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -4439,31 +4725,37 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>25800</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>24400</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>21400</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>18600</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -4516,8 +4808,14 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4891,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4974,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,85 +5057,97 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1710800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1598900</v>
+      </c>
+      <c r="F66" s="3">
         <v>1692900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1569100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1691600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1589500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1604400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1584800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1827900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1721600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1737000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1599200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1728500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1558400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1559800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1346700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1403600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1302400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1271200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1163800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1226200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1345000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1253800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1160600</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA66" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5175,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5254,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5337,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5420,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,85 +5503,97 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>192800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>187700</v>
+      </c>
+      <c r="F72" s="3">
         <v>184900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>180200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>177000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>173000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>168500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>162500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>156300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>151100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>148700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>148400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>142200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>140800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>144400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>143000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>141100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>139700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>139000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>138100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>134300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>135400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>130400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>125600</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA72" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5669,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5752,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,85 +5835,97 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>303800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>296500</v>
+      </c>
+      <c r="F76" s="3">
         <v>289000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>283800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>271800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>266700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>259900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>249700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>241700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>242600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>237100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>244000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>239100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>237800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>228700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>227400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>225400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>224000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>228500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>228000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>223800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>135000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>131800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>126400</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA76" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +6001,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F81" s="3">
         <v>4700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>3200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>3400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>4500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>6000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>6200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>5200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>2400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>6300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>1400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-3600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>1900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>1500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>2900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>5000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>4800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>4800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>4400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,16 +6207,18 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E83" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="F83" s="3">
         <v>700</v>
@@ -5832,7 +6230,7 @@
         <v>700</v>
       </c>
       <c r="I83" s="3">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="J83" s="3">
         <v>700</v>
@@ -5868,13 +6266,13 @@
         <v>700</v>
       </c>
       <c r="U83" s="3">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="V83" s="3">
         <v>700</v>
       </c>
       <c r="W83" s="3">
-        <v>700</v>
+        <v>1500</v>
       </c>
       <c r="X83" s="3">
         <v>700</v>
@@ -5888,8 +6286,14 @@
       <c r="AA83" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6369,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6452,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6535,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6618,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,85 +6701,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F89" s="3">
         <v>3300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>12400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>13600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>2400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>8000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>21400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>22800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>5900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>5400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>21500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>7800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-2000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>9400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-18400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>11000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-1800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>7200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,8 +6819,10 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6391,73 +6833,79 @@
         <v>-200</v>
       </c>
       <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
       </c>
       <c r="M91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O91" s="3">
         <v>-400</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-300</v>
       </c>
       <c r="P91" s="3">
         <v>-200</v>
       </c>
       <c r="Q91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-500</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-500</v>
       </c>
       <c r="X91" s="3">
         <v>-500</v>
       </c>
       <c r="Y91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6981,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,85 +7064,97 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-59300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-21000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>37200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-39000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>11200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-29100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-20000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-77000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-81100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-38400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-6300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-22300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-7700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-99400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-17700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-57500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-12600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-39300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-16000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-14900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>2600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-62600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-10100</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,31 +7182,33 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6793,8 +7261,14 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7344,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7427,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,108 +7510,120 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>117200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-95100</v>
+      </c>
+      <c r="F100" s="3">
         <v>124600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-113100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>92600</v>
       </c>
-      <c r="G100" s="3">
-        <v>-19400</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="J100" s="3">
         <v>24500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-237900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>95800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-29000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>131200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-123100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>170000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>210500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-56300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>107600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>14800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>106300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-86900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-24400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>90000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>97600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-89400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>83500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-30300</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7178,81 +7676,93 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-81400</v>
+      </c>
+      <c r="F102" s="3">
         <v>106900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-76900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>66100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>5400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-255600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>26800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-88700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>115600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-129400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>153600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-3600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>132600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-66200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>105300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-33300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>75300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-115200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-41300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>73300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>100300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-92000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>28100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-37400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PBFS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PBFS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
   <si>
     <t>PBFS</t>
   </si>
@@ -656,212 +656,218 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E8" s="3">
         <v>22900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>21500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>18700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>18000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>13300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>28400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>14600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>14200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>13600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>13300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>13000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -943,35 +949,38 @@
       <c r="AC9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E10" s="3">
         <v>22900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>20100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>21500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>18700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>19100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>20800</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1026,8 +1035,11 @@
       <c r="AC10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,8 +1069,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1140,8 +1153,11 @@
       <c r="AC12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,34 +1239,37 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>-6000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1306,8 +1325,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1324,7 +1346,7 @@
         <v>600</v>
       </c>
       <c r="H15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="I15" s="3">
         <v>700</v>
@@ -1333,7 +1355,7 @@
         <v>700</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1374,8 +1396,8 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>5</v>
+      <c r="Y15" s="3">
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>5</v>
@@ -1389,8 +1411,11 @@
       <c r="AC15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1442,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E17" s="3">
         <v>14400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>15500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4700</v>
-      </c>
-      <c r="X17" s="3">
-        <v>1900</v>
       </c>
       <c r="Y17" s="3">
         <v>1900</v>
       </c>
       <c r="Z17" s="3">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="AA17" s="3">
         <v>1700</v>
       </c>
       <c r="AB17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AC17" s="3">
         <v>1600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E18" s="3">
         <v>8500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>10000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>8800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>9500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>23700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>12700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>12300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>11600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,13 +1646,14 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>300</v>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E20" s="3">
         <v>300</v>
@@ -1638,150 +1671,156 @@
         <v>300</v>
       </c>
       <c r="J20" s="3">
+        <v>300</v>
+      </c>
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-9600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-9500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-9400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-12900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-7600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-6600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-7900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-7100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-8500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-20400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-14300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E21" s="3">
         <v>8800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3200</v>
-      </c>
-      <c r="T21" s="3">
-        <v>2400</v>
       </c>
       <c r="U21" s="3">
         <v>2400</v>
       </c>
       <c r="V21" s="3">
+        <v>2400</v>
+      </c>
+      <c r="W21" s="3">
         <v>1800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>7200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>6900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>6200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>6300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1806,8 +1845,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1863,174 +1902,183 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E23" s="3">
         <v>8200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2400</v>
-      </c>
-      <c r="T23" s="3">
-        <v>1700</v>
       </c>
       <c r="U23" s="3">
         <v>1700</v>
       </c>
       <c r="V23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="W23" s="3">
         <v>1100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>900</v>
+      </c>
+      <c r="E24" s="3">
         <v>1900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1800</v>
-      </c>
-      <c r="P24" s="3">
-        <v>400</v>
       </c>
       <c r="Q24" s="3">
         <v>400</v>
       </c>
       <c r="R24" s="3">
+        <v>400</v>
+      </c>
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>300</v>
-      </c>
-      <c r="U24" s="3">
-        <v>200</v>
       </c>
       <c r="V24" s="3">
         <v>200</v>
       </c>
       <c r="W24" s="3">
+        <v>200</v>
+      </c>
+      <c r="X24" s="3">
         <v>400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2160,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E26" s="3">
         <v>6300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>5000</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>4800</v>
       </c>
       <c r="AA26" s="3">
         <v>4800</v>
       </c>
       <c r="AB26" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AC26" s="3">
         <v>4400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E27" s="3">
         <v>6300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5000</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>4800</v>
       </c>
       <c r="AA27" s="3">
         <v>4800</v>
       </c>
       <c r="AB27" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AC27" s="3">
         <v>4400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2418,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2435,17 +2495,20 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2590,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,13 +2676,16 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-300</v>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E32" s="3">
         <v>-300</v>
@@ -2634,150 +2703,156 @@
         <v>-300</v>
       </c>
       <c r="J32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>9600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>9500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>9400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>8200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>12900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>7600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>6600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>7900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>7100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>8500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>20400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>14300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>5800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>5700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>6100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>5800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E33" s="3">
         <v>6300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5000</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>4800</v>
       </c>
       <c r="AA33" s="3">
         <v>4800</v>
       </c>
       <c r="AB33" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AC33" s="3">
         <v>4400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2934,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E35" s="3">
         <v>6300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5000</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>4800</v>
       </c>
       <c r="AA35" s="3">
         <v>4800</v>
       </c>
       <c r="AB35" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AC35" s="3">
         <v>4400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3145,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,174 +3177,181 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="3">
         <v>225000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>165200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>246500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>139600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>216500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>150500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>145100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>33500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>52600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>29800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>32800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>26300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>58400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>24500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>25500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>34500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>37400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>21200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>22900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>24600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>41600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>48400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>38300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>28000</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>200</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>114900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>351400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>347300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>433200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>323900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>421500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>301700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>304200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>162500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>225700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>136700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>209200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>106800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>167100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>182600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>119300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>30700</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3281,12 +3373,12 @@
       <c r="I43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K43" s="3">
         <v>5000</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -3341,8 +3433,11 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3367,8 +3462,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3424,35 +3519,38 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3">
         <v>7700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7600</v>
-      </c>
-      <c r="F45" s="3">
-        <v>7700</v>
       </c>
       <c r="G45" s="3">
         <v>7700</v>
       </c>
       <c r="H45" s="3">
+        <v>7700</v>
+      </c>
+      <c r="I45" s="3">
         <v>7100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8200</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -3507,34 +3605,37 @@
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E46" s="3">
         <v>233000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>172900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>254400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>147500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>223700</v>
-      </c>
-      <c r="I46" s="3">
-        <v>158400</v>
       </c>
       <c r="J46" s="3">
         <v>158400</v>
       </c>
       <c r="K46" s="3">
-        <v>0</v>
+        <v>158400</v>
       </c>
       <c r="L46" s="3">
         <v>0</v>
@@ -3590,35 +3691,38 @@
       <c r="AC46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3">
         <v>290800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>286000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>321600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>348000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>439900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>459200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>531500</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -3673,174 +3777,183 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="3">
         <v>39700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>40100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>40700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>41100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>41500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>41600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>42200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>42600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>43300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>37300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>37800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>38200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>38500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>38900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>39300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>39700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>40300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>40900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>41300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>41500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>41600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>41700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>41800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>42000</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>13700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11200</v>
-      </c>
-      <c r="P49" s="3">
-        <v>9100</v>
       </c>
       <c r="Q49" s="3">
         <v>9100</v>
       </c>
       <c r="R49" s="3">
+        <v>9100</v>
+      </c>
+      <c r="S49" s="3">
         <v>9200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9400</v>
-      </c>
-      <c r="U49" s="3">
-        <v>9500</v>
       </c>
       <c r="V49" s="3">
         <v>9500</v>
       </c>
       <c r="W49" s="3">
+        <v>9500</v>
+      </c>
+      <c r="X49" s="3">
         <v>9600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>10000</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4035,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,35 +4121,38 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3">
         <v>37700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>38200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>39000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>38500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>40600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>36700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>35000</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -4088,8 +4207,11 @@
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4293,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E54" s="3">
         <v>2014600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1895400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1981800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1852900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1963400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1856200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1864300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1834500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2069600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1964200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1974100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1843200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1967700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1796300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1788500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1574200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1629000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1526400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1499700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1391800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1449900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1480000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1385500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1287000</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4413,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,35 +4445,36 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3">
         <v>1675300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1550300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1648000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1522100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1638800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1541900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1564600</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
@@ -4369,15 +4499,15 @@
       <c r="S57" s="3">
         <v>0</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U57" s="3">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V57" s="3">
         <v>7800</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4390,8 +4520,8 @@
       <c r="Z57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA57" s="3">
-        <v>0</v>
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB57" s="3">
         <v>0</v>
@@ -4399,35 +4529,38 @@
       <c r="AC57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>9700</v>
       </c>
-      <c r="E58" s="3">
-        <v>17500</v>
-      </c>
       <c r="F58" s="3">
+        <v>22900</v>
+      </c>
+      <c r="G58" s="3">
         <v>18000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>34100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>23100</v>
       </c>
-      <c r="I58" s="3">
-        <v>18800</v>
-      </c>
       <c r="J58" s="3">
+        <v>25300</v>
+      </c>
+      <c r="K58" s="3">
         <v>15400</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4482,8 +4615,11 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4508,12 +4644,12 @@
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L59" s="3">
         <v>5900</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4529,8 +4665,8 @@
       <c r="Q59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
+      <c r="R59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S59" s="3">
         <v>0</v>
@@ -4565,35 +4701,38 @@
       <c r="AC59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E60" s="3">
         <v>1685000</v>
       </c>
-      <c r="E60" s="3">
-        <v>1567800</v>
-      </c>
       <c r="F60" s="3">
+        <v>1573200</v>
+      </c>
+      <c r="G60" s="3">
         <v>1666000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1556200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1661900</v>
       </c>
-      <c r="I60" s="3">
-        <v>1560700</v>
-      </c>
       <c r="J60" s="3">
+        <v>1567100</v>
+      </c>
+      <c r="K60" s="3">
         <v>1580000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -4648,8 +4787,11 @@
       <c r="AC60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4657,29 +4799,29 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>5500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5700</v>
       </c>
-      <c r="I61" s="3">
-        <v>6400</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>5800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>800</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4731,35 +4873,38 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="3">
         <v>25800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>24400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>21400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>24000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>21000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>18600</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -4814,8 +4959,11 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5045,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5131,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5217,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E66" s="3">
         <v>1710800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1598900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1692900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1569100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1691600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1589500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1604400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1584800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1827900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1721600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1737000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1599200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1728500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1558400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1559800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1346700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1403600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1302400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1271200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1163800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1226200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1345000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1253800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1160600</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5337,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5421,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5507,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5593,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5679,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3">
         <v>192800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>187700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>184900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>180200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>177000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>173000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>168500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>162500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>156300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>151100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>148700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>148400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>142200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>140800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>144400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>143000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>141100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>139700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>139000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>138100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>134300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>135400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>130400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>125600</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5851,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5937,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,8 +6023,11 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -5850,82 +6035,85 @@
         <v>303800</v>
       </c>
       <c r="E76" s="3">
+        <v>303800</v>
+      </c>
+      <c r="F76" s="3">
         <v>296500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>289000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>283800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>271800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>266700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>259900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>249700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>241700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>242600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>237100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>244000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>239100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>237800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>228700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>227400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>225400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>224000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>228500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>228000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>223800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>135000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>131800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>126400</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6195,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E81" s="3">
         <v>6300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5000</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>4800</v>
       </c>
       <c r="AA81" s="3">
         <v>4800</v>
       </c>
       <c r="AB81" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AC81" s="3">
         <v>4400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,19 +6406,20 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3">
         <v>700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>300</v>
-      </c>
-      <c r="F83" s="3">
-        <v>700</v>
       </c>
       <c r="G83" s="3">
         <v>700</v>
@@ -6230,10 +6428,10 @@
         <v>700</v>
       </c>
       <c r="I83" s="3">
+        <v>700</v>
+      </c>
+      <c r="J83" s="3">
         <v>300</v>
-      </c>
-      <c r="J83" s="3">
-        <v>700</v>
       </c>
       <c r="K83" s="3">
         <v>700</v>
@@ -6272,10 +6470,10 @@
         <v>700</v>
       </c>
       <c r="W83" s="3">
+        <v>700</v>
+      </c>
+      <c r="X83" s="3">
         <v>1500</v>
-      </c>
-      <c r="X83" s="3">
-        <v>700</v>
       </c>
       <c r="Y83" s="3">
         <v>700</v>
@@ -6292,8 +6490,11 @@
       <c r="AC83" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6576,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6662,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6748,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6834,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6920,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3">
         <v>1900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>12400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13600</v>
-      </c>
-      <c r="J89" s="3">
-        <v>2400</v>
       </c>
       <c r="K89" s="3">
         <v>2400</v>
       </c>
       <c r="L89" s="3">
+        <v>2400</v>
+      </c>
+      <c r="M89" s="3">
         <v>8000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>21400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>22800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>21500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>7800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>9400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-18400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>11000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,37 +7040,38 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
@@ -6860,34 +7080,34 @@
         <v>-100</v>
       </c>
       <c r="O91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-500</v>
       </c>
       <c r="Y91" s="3">
         <v>-500</v>
@@ -6896,16 +7116,19 @@
         <v>-500</v>
       </c>
       <c r="AA91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-700</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-600</v>
       </c>
       <c r="AC91" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7210,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,91 +7296,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3">
         <v>-59300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>4700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>37200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-39000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>11200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-29100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-20000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-77000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-81100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-38400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-22300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-99400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-17700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-57500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-12600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-39300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-14900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>2600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-62600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-10100</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7416,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7210,8 +7443,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7267,8 +7500,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7586,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7672,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,91 +7758,97 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3">
         <v>117200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-95100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>124600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-113100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>92600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-19300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>24500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-237900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>95800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-29000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>131200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-123100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>170000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>210500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-56300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>107600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>14800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>106300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-86900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-24400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>90000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>97600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-89400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>83500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-30300</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7625,8 +7873,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7682,87 +7930,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>59800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-81400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>106900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-76900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>66100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-255600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>26800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-88700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>115600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-129400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>153600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>132600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-66200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>105300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-33300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>75300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-115200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-41300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>73300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>100300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-92000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>28100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-37400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PBFS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PBFS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
   <si>
     <t>PBFS</t>
   </si>
@@ -656,218 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
-        <v>45199</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E8" s="3">
         <v>21200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>22900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>21500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
+        <v>21500</v>
+      </c>
+      <c r="J8" s="3">
         <v>13900</v>
       </c>
-      <c r="I8" s="3">
-        <v>18700</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>18000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>13300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>28400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>14600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>14200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>13600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>13300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>13000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -952,38 +959,41 @@
       <c r="AD9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E10" s="3">
         <v>21200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>22900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>20100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>21500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>21500</v>
+      </c>
+      <c r="J10" s="3">
         <v>13900</v>
       </c>
-      <c r="I10" s="3">
-        <v>18700</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>19100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>20800</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1038,8 +1048,11 @@
       <c r="AD10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1070,8 +1083,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1156,8 +1170,11 @@
       <c r="AD12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1242,8 +1259,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1253,26 +1273,26 @@
       <c r="E14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>-6000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1328,8 +1348,11 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1349,16 +1372,16 @@
         <v>600</v>
       </c>
       <c r="I15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="J15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="K15" s="3">
         <v>700</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1399,8 +1422,8 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>5</v>
+      <c r="Z15" s="3">
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="s">
         <v>5</v>
@@ -1414,8 +1437,11 @@
       <c r="AD15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E17" s="3">
         <v>17000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>15200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>15200</v>
+      </c>
+      <c r="J17" s="3">
         <v>15500</v>
       </c>
-      <c r="I17" s="3">
-        <v>14100</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4700</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>1900</v>
       </c>
       <c r="Z17" s="3">
         <v>1900</v>
       </c>
       <c r="AA17" s="3">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="AB17" s="3">
         <v>1700</v>
       </c>
       <c r="AC17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AD17" s="3">
         <v>1600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E18" s="3">
         <v>4200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>8500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>6300</v>
+      </c>
+      <c r="J18" s="3">
         <v>-1700</v>
       </c>
-      <c r="I18" s="3">
-        <v>4600</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>17600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>10500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>8800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>9500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>23700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>12700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>12300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>11900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>11400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,16 +1680,17 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="3">
-        <v>300</v>
+      <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F20" s="3">
         <v>300</v>
@@ -1674,153 +1708,159 @@
         <v>300</v>
       </c>
       <c r="K20" s="3">
+        <v>300</v>
+      </c>
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-9600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-9500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-12900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-7600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-6600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-7900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-7100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-8500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-20400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-14300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-5800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J21" s="3">
         <v>-1300</v>
       </c>
-      <c r="I21" s="3">
-        <v>5000</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3200</v>
-      </c>
-      <c r="U21" s="3">
-        <v>2400</v>
       </c>
       <c r="V21" s="3">
         <v>2400</v>
       </c>
       <c r="W21" s="3">
+        <v>2400</v>
+      </c>
+      <c r="X21" s="3">
         <v>1800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>7200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>6900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>6200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>6300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1848,8 +1888,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1905,180 +1945,189 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E23" s="3">
         <v>4200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>8200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>6100</v>
+      </c>
+      <c r="J23" s="3">
         <v>4000</v>
       </c>
-      <c r="I23" s="3">
-        <v>4300</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2400</v>
-      </c>
-      <c r="U23" s="3">
-        <v>1700</v>
       </c>
       <c r="V23" s="3">
         <v>1700</v>
       </c>
       <c r="W23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="X23" s="3">
         <v>1100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>5700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E24" s="3">
         <v>900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J24" s="3">
         <v>800</v>
       </c>
-      <c r="I24" s="3">
-        <v>900</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1800</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>400</v>
       </c>
       <c r="R24" s="3">
         <v>400</v>
       </c>
       <c r="S24" s="3">
+        <v>400</v>
+      </c>
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
-      </c>
-      <c r="V24" s="3">
-        <v>200</v>
       </c>
       <c r="W24" s="3">
         <v>200</v>
       </c>
       <c r="X24" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y24" s="3">
         <v>400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E26" s="3">
         <v>3300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J26" s="3">
         <v>3200</v>
       </c>
-      <c r="I26" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>5000</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>4800</v>
       </c>
       <c r="AB26" s="3">
         <v>4800</v>
       </c>
       <c r="AC26" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AD26" s="3">
         <v>4400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E27" s="3">
         <v>3300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J27" s="3">
         <v>3200</v>
       </c>
-      <c r="I27" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>5000</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>4800</v>
       </c>
       <c r="AB27" s="3">
         <v>4800</v>
       </c>
       <c r="AC27" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AD27" s="3">
         <v>4400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2498,17 +2559,20 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,16 +2746,19 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-300</v>
+      <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F32" s="3">
         <v>-300</v>
@@ -2706,153 +2776,159 @@
         <v>-300</v>
       </c>
       <c r="K32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>9600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>9500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>12900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>7600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>6600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>7900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>7100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>8500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>20400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>14300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>5800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>5700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>6100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>5800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E33" s="3">
         <v>3300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J33" s="3">
         <v>3200</v>
       </c>
-      <c r="I33" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>5000</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>4800</v>
       </c>
       <c r="AB33" s="3">
         <v>4800</v>
       </c>
       <c r="AC33" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AD33" s="3">
         <v>4400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E35" s="3">
         <v>3300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J35" s="3">
         <v>3200</v>
       </c>
-      <c r="I35" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>5000</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>4800</v>
       </c>
       <c r="AB35" s="3">
         <v>4800</v>
       </c>
       <c r="AC35" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AD35" s="3">
         <v>4400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
-        <v>45199</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,94 +3264,98 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E41" s="3">
+      <c r="D41" s="3">
+        <v>139600</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" s="3">
         <v>225000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>165200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>246500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
+        <v>246500</v>
+      </c>
+      <c r="J41" s="3">
         <v>139600</v>
       </c>
-      <c r="I41" s="3">
-        <v>216500</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>150500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>145100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>33500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>52600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>29800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>32800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>26300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>58400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>24500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>25500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>34500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>37400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>21200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>22900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>24600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>41600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>48400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>38300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>28000</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3273,85 +3363,88 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
+        <v>100</v>
+      </c>
+      <c r="J42" s="3">
         <v>200</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>114900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>351400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>347300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>433200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>323900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>421500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>301700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>304200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>162500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>225700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>136700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>209200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>106800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>167100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>182600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>119300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>30700</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3376,12 +3469,12 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L43" s="3">
         <v>5000</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -3436,8 +3529,11 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3465,8 +3561,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3522,38 +3618,41 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3">
         <v>7700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7600</v>
-      </c>
-      <c r="G45" s="3">
-        <v>7700</v>
       </c>
       <c r="H45" s="3">
         <v>7700</v>
       </c>
       <c r="I45" s="3">
-        <v>7100</v>
+        <v>7700</v>
       </c>
       <c r="J45" s="3">
+        <v>7700</v>
+      </c>
+      <c r="K45" s="3">
         <v>7200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8200</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -3608,37 +3707,40 @@
       <c r="AD45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E46" s="3">
+      <c r="D46" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F46" s="3">
         <v>233000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>172900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>254400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
+        <v>254400</v>
+      </c>
+      <c r="J46" s="3">
         <v>147500</v>
-      </c>
-      <c r="I46" s="3">
-        <v>223700</v>
-      </c>
-      <c r="J46" s="3">
-        <v>158400</v>
       </c>
       <c r="K46" s="3">
         <v>158400</v>
       </c>
       <c r="L46" s="3">
-        <v>0</v>
+        <v>158400</v>
       </c>
       <c r="M46" s="3">
         <v>0</v>
@@ -3694,38 +3796,41 @@
       <c r="AD46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E47" s="3">
+      <c r="D47" s="3">
+        <v>346100</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3">
         <v>290800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>286000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>321600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
+        <v>321600</v>
+      </c>
+      <c r="J47" s="3">
         <v>348000</v>
       </c>
-      <c r="I47" s="3">
-        <v>439900</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>459200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>531500</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -3780,180 +3885,189 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E48" s="3">
+      <c r="D48" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3">
         <v>39700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>40100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>40700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
+        <v>40700</v>
+      </c>
+      <c r="J48" s="3">
         <v>41100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
+        <v>41600</v>
+      </c>
+      <c r="L48" s="3">
+        <v>42200</v>
+      </c>
+      <c r="M48" s="3">
+        <v>42600</v>
+      </c>
+      <c r="N48" s="3">
+        <v>43300</v>
+      </c>
+      <c r="O48" s="3">
+        <v>37300</v>
+      </c>
+      <c r="P48" s="3">
+        <v>37800</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>38200</v>
+      </c>
+      <c r="R48" s="3">
+        <v>38500</v>
+      </c>
+      <c r="S48" s="3">
+        <v>38900</v>
+      </c>
+      <c r="T48" s="3">
+        <v>39300</v>
+      </c>
+      <c r="U48" s="3">
+        <v>39700</v>
+      </c>
+      <c r="V48" s="3">
+        <v>40300</v>
+      </c>
+      <c r="W48" s="3">
+        <v>40900</v>
+      </c>
+      <c r="X48" s="3">
+        <v>41300</v>
+      </c>
+      <c r="Y48" s="3">
         <v>41500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="Z48" s="3">
         <v>41600</v>
       </c>
-      <c r="K48" s="3">
-        <v>42200</v>
-      </c>
-      <c r="L48" s="3">
-        <v>42600</v>
-      </c>
-      <c r="M48" s="3">
-        <v>43300</v>
-      </c>
-      <c r="N48" s="3">
-        <v>37300</v>
-      </c>
-      <c r="O48" s="3">
-        <v>37800</v>
-      </c>
-      <c r="P48" s="3">
-        <v>38200</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>38500</v>
-      </c>
-      <c r="R48" s="3">
-        <v>38900</v>
-      </c>
-      <c r="S48" s="3">
-        <v>39300</v>
-      </c>
-      <c r="T48" s="3">
-        <v>39700</v>
-      </c>
-      <c r="U48" s="3">
-        <v>40300</v>
-      </c>
-      <c r="V48" s="3">
-        <v>40900</v>
-      </c>
-      <c r="W48" s="3">
-        <v>41300</v>
-      </c>
-      <c r="X48" s="3">
-        <v>41500</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>41600</v>
-      </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>41700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>41800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>42000</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>13500</v>
       </c>
       <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>13700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
+        <v>14000</v>
+      </c>
+      <c r="J49" s="3">
         <v>14100</v>
       </c>
-      <c r="I49" s="3">
-        <v>14200</v>
-      </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11200</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>9100</v>
       </c>
       <c r="R49" s="3">
         <v>9100</v>
       </c>
       <c r="S49" s="3">
+        <v>9100</v>
+      </c>
+      <c r="T49" s="3">
         <v>9200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9400</v>
-      </c>
-      <c r="V49" s="3">
-        <v>9500</v>
       </c>
       <c r="W49" s="3">
         <v>9500</v>
       </c>
       <c r="X49" s="3">
+        <v>9500</v>
+      </c>
+      <c r="Y49" s="3">
         <v>9600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>9900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>10000</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,38 +4241,41 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3">
         <v>37700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>38200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>39000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
+        <v>39000</v>
+      </c>
+      <c r="J52" s="3">
         <v>38500</v>
       </c>
-      <c r="I52" s="3">
-        <v>40600</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>36700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>35000</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -4210,8 +4330,11 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,94 +4419,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E54" s="3">
+      <c r="D54" s="3">
+        <v>2069000</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" s="3">
         <v>2014600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1895400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1981800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
+        <v>1981800</v>
+      </c>
+      <c r="J54" s="3">
         <v>1852900</v>
       </c>
-      <c r="I54" s="3">
-        <v>1963400</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1856200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1864300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1834500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2069600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1964200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1974100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1843200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1967700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1796300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1788500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1574200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1629000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1526400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1499700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1391800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1449900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1480000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1385500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1287000</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,38 +4576,39 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E57" s="3">
+      <c r="D57" s="3">
+        <v>1721600</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="3">
         <v>1675300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1550300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1648000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>1648000</v>
+      </c>
+      <c r="J57" s="3">
         <v>1522100</v>
       </c>
-      <c r="I57" s="3">
-        <v>1638800</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1541900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1564600</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
@@ -4502,15 +4633,15 @@
       <c r="T57" s="3">
         <v>0</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V57" s="3">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W57" s="3">
         <v>7800</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4523,8 +4654,8 @@
       <c r="AA57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB57" s="3">
-        <v>0</v>
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC57" s="3">
         <v>0</v>
@@ -4532,38 +4663,41 @@
       <c r="AD57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>10700</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>9700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>22900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>18000</v>
+      </c>
+      <c r="J58" s="3">
         <v>34100</v>
       </c>
-      <c r="I58" s="3">
-        <v>23100</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>25300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>15400</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4618,8 +4752,11 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4647,12 +4784,12 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M59" s="3">
         <v>5900</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4668,8 +4805,8 @@
       <c r="R59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S59" s="3">
-        <v>0</v>
+      <c r="S59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T59" s="3">
         <v>0</v>
@@ -4704,38 +4841,41 @@
       <c r="AD59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E60" s="3">
+      <c r="D60" s="3">
+        <v>1732400</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F60" s="3">
         <v>1685000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1573200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1666000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>1666000</v>
+      </c>
+      <c r="J60" s="3">
         <v>1556200</v>
       </c>
-      <c r="I60" s="3">
-        <v>1661900</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1567100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1580000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -4790,8 +4930,11 @@
       <c r="AD60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4805,26 +4948,26 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>5500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
+        <v>5500</v>
+      </c>
+      <c r="J61" s="3">
         <v>5600</v>
       </c>
-      <c r="I61" s="3">
-        <v>5700</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>5800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>800</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4876,38 +5019,41 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E62" s="3">
+      <c r="D62" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3">
         <v>25800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>24400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>21400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
+        <v>21400</v>
+      </c>
+      <c r="J62" s="3">
         <v>7300</v>
       </c>
-      <c r="I62" s="3">
-        <v>24000</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>21000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>18600</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -4962,8 +5108,11 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,94 +5375,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E66" s="3">
+      <c r="D66" s="3">
+        <v>1758300</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" s="3">
         <v>1710800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1598900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1692900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
+        <v>1692900</v>
+      </c>
+      <c r="J66" s="3">
         <v>1569100</v>
       </c>
-      <c r="I66" s="3">
-        <v>1691600</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1589500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1604400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1584800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1827900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1721600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1737000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1599200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1728500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1558400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1559800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1346700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1403600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1302400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1271200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1163800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1226200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1345000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1253800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1160600</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,94 +5853,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3">
+        <v>198400</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F72" s="3">
         <v>192800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>187700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>184900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
+        <v>184900</v>
+      </c>
+      <c r="J72" s="3">
         <v>180200</v>
       </c>
-      <c r="I72" s="3">
-        <v>177000</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>173000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>168500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>162500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>156300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>151100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>148700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>148400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>142200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>140800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>144400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>143000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>141100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>139700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>139000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>138100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>134300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>135400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>130400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>125600</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,94 +6209,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>303800</v>
+        <v>310700</v>
       </c>
       <c r="E76" s="3">
         <v>303800</v>
       </c>
       <c r="F76" s="3">
+        <v>303800</v>
+      </c>
+      <c r="G76" s="3">
         <v>296500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>289000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
+        <v>289000</v>
+      </c>
+      <c r="J76" s="3">
         <v>283800</v>
       </c>
-      <c r="I76" s="3">
-        <v>271800</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>266700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>259900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>249700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>241700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>242600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>237100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>244000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>239100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>237800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>228700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>227400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>225400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>224000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>228500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>228000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>223800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>135000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>131800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>126400</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
-        <v>45199</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E81" s="3">
         <v>3300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J81" s="3">
         <v>3200</v>
       </c>
-      <c r="I81" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>5000</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>4800</v>
       </c>
       <c r="AB81" s="3">
         <v>4800</v>
       </c>
       <c r="AC81" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AD81" s="3">
         <v>4400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,8 +6605,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6416,25 +6615,25 @@
         <v>600</v>
       </c>
       <c r="E83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F83" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="G83" s="3">
         <v>700</v>
       </c>
       <c r="H83" s="3">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="I83" s="3">
         <v>700</v>
       </c>
       <c r="J83" s="3">
+        <v>700</v>
+      </c>
+      <c r="K83" s="3">
         <v>300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>700</v>
       </c>
       <c r="L83" s="3">
         <v>700</v>
@@ -6473,10 +6672,10 @@
         <v>700</v>
       </c>
       <c r="X83" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y83" s="3">
         <v>1500</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>700</v>
       </c>
       <c r="Z83" s="3">
         <v>700</v>
@@ -6493,8 +6692,11 @@
       <c r="AD83" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,94 +7137,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E89" s="3">
+      <c r="D89" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3">
         <v>1900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J89" s="3">
         <v>-900</v>
       </c>
-      <c r="I89" s="3">
-        <v>12400</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13600</v>
-      </c>
-      <c r="K89" s="3">
-        <v>2400</v>
       </c>
       <c r="L89" s="3">
         <v>2400</v>
       </c>
       <c r="M89" s="3">
+        <v>2400</v>
+      </c>
+      <c r="N89" s="3">
         <v>8000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>21400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>22800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>21500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>7800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>9400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-18400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>11000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>7200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,40 +7261,41 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E91" s="3">
+      <c r="D91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
@@ -7083,34 +7304,34 @@
         <v>-100</v>
       </c>
       <c r="P91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-500</v>
       </c>
       <c r="Z91" s="3">
         <v>-500</v>
@@ -7119,16 +7340,19 @@
         <v>-500</v>
       </c>
       <c r="AB91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-700</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-600</v>
       </c>
       <c r="AD91" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,94 +7526,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3">
+      <c r="D94" s="3">
+        <v>-45700</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3">
         <v>-59300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>4700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-21000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="J94" s="3">
         <v>37200</v>
       </c>
-      <c r="I94" s="3">
-        <v>-39000</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>11200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-29100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-20000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-77000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-81100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-38400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-22300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-99400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-17700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-57500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-12600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-39300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-16000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-14900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>2600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-62600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-10100</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7446,8 +7680,8 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7503,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,94 +8004,100 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E100" s="3">
+      <c r="D100" s="3">
+        <v>92300</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3">
         <v>117200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-95100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>124600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>124600</v>
+      </c>
+      <c r="J100" s="3">
         <v>-113100</v>
       </c>
-      <c r="I100" s="3">
-        <v>92600</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-19300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>24500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-237900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>95800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-29000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>131200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-123100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>170000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>210500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-56300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>107600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>14800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>106300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-86900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-24400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>90000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>97600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-89400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>83500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-30300</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7876,8 +8125,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7933,90 +8182,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>43100</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>59800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-81400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>106900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>106900</v>
+      </c>
+      <c r="J102" s="3">
         <v>-76900</v>
       </c>
-      <c r="I102" s="3">
-        <v>66100</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-255600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>26800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-88700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>115600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-129400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>153600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>132600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-66200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>105300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-33300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>75300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-115200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-41300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>73300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>100300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-92000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>28100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-37400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PBFS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PBFS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="92">
   <si>
     <t>PBFS</t>
   </si>
@@ -656,225 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="J7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
-        <v>45382</v>
-      </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E8" s="3">
         <v>22000</v>
       </c>
-      <c r="E8" s="3">
-        <v>21200</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3">
         <v>22900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
+        <v>20100</v>
+      </c>
+      <c r="J8" s="3">
         <v>21500</v>
       </c>
-      <c r="I8" s="3">
-        <v>21500</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>13300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>28400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>14600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>14200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>13600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>13300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>13000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -962,41 +969,44 @@
       <c r="AE9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E10" s="3">
         <v>22000</v>
       </c>
-      <c r="E10" s="3">
-        <v>21200</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="F10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3">
         <v>22900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>20100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>20100</v>
+      </c>
+      <c r="J10" s="3">
         <v>21500</v>
       </c>
-      <c r="I10" s="3">
-        <v>21500</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>13900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>19100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>20800</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1051,8 +1061,11 @@
       <c r="AE10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1276,26 +1296,26 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>-6000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1351,8 +1371,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1363,7 +1386,7 @@
         <v>600</v>
       </c>
       <c r="F15" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
         <v>600</v>
@@ -1378,13 +1401,13 @@
         <v>600</v>
       </c>
       <c r="K15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="L15" s="3">
         <v>700</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1425,8 +1448,8 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>5</v>
+      <c r="AA15" s="3">
+        <v>0</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>5</v>
@@ -1440,8 +1463,11 @@
       <c r="AE15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E17" s="3">
         <v>14400</v>
       </c>
-      <c r="E17" s="3">
-        <v>17000</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="F17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3">
         <v>14400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>14800</v>
+      </c>
+      <c r="J17" s="3">
         <v>15200</v>
       </c>
-      <c r="I17" s="3">
-        <v>15200</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4700</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>1900</v>
       </c>
       <c r="AA17" s="3">
         <v>1900</v>
       </c>
       <c r="AB17" s="3">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="AC17" s="3">
         <v>1700</v>
       </c>
       <c r="AD17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AE17" s="3">
         <v>1600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E18" s="3">
         <v>7600</v>
       </c>
-      <c r="E18" s="3">
-        <v>4200</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="F18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3">
         <v>8500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>5300</v>
+      </c>
+      <c r="J18" s="3">
         <v>6300</v>
       </c>
-      <c r="I18" s="3">
-        <v>6300</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>17600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>12500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>10000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>9600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>8800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>9500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>23700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>12700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>12300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>11600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>11400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,19 +1714,20 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="3">
-        <v>300</v>
+      <c r="E20" s="3">
+        <v>200</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G20" s="3">
         <v>300</v>
@@ -1711,156 +1745,162 @@
         <v>300</v>
       </c>
       <c r="L20" s="3">
+        <v>300</v>
+      </c>
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-9600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-8200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-12900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-7600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-6600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-7900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-8500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-20400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-14300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-5800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-5700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-5800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E21" s="3">
         <v>8000</v>
       </c>
-      <c r="E21" s="3">
-        <v>4800</v>
-      </c>
       <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
         <v>8800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>5700</v>
+      </c>
+      <c r="J21" s="3">
         <v>6700</v>
       </c>
-      <c r="I21" s="3">
-        <v>6700</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3200</v>
-      </c>
-      <c r="V21" s="3">
-        <v>2400</v>
       </c>
       <c r="W21" s="3">
         <v>2400</v>
       </c>
       <c r="X21" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Y21" s="3">
         <v>1800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>7200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>6900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>6200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>6300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1891,8 +1931,8 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1948,97 +1988,103 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E23" s="3">
         <v>7400</v>
       </c>
-      <c r="E23" s="3">
-        <v>4200</v>
-      </c>
-      <c r="F23" s="3">
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="3">
         <v>8200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J23" s="3">
         <v>6100</v>
       </c>
-      <c r="I23" s="3">
-        <v>6100</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2400</v>
-      </c>
-      <c r="V23" s="3">
-        <v>1700</v>
       </c>
       <c r="W23" s="3">
         <v>1700</v>
       </c>
       <c r="X23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Y23" s="3">
         <v>1100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>5500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2046,88 +2092,91 @@
         <v>1700</v>
       </c>
       <c r="E24" s="3">
-        <v>900</v>
-      </c>
-      <c r="F24" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3">
         <v>1900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J24" s="3">
         <v>1300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
+        <v>800</v>
+      </c>
+      <c r="L24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O24" s="3">
         <v>1300</v>
       </c>
-      <c r="J24" s="3">
-        <v>800</v>
-      </c>
-      <c r="K24" s="3">
-        <v>1200</v>
-      </c>
-      <c r="L24" s="3">
-        <v>1600</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="P24" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>200</v>
+      </c>
+      <c r="R24" s="3">
         <v>1800</v>
-      </c>
-      <c r="N24" s="3">
-        <v>1300</v>
-      </c>
-      <c r="O24" s="3">
-        <v>700</v>
-      </c>
-      <c r="P24" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>1800</v>
-      </c>
-      <c r="R24" s="3">
-        <v>400</v>
       </c>
       <c r="S24" s="3">
         <v>400</v>
       </c>
       <c r="T24" s="3">
+        <v>400</v>
+      </c>
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>300</v>
-      </c>
-      <c r="W24" s="3">
-        <v>200</v>
       </c>
       <c r="X24" s="3">
         <v>200</v>
       </c>
       <c r="Y24" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z24" s="3">
         <v>400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E26" s="3">
         <v>5800</v>
       </c>
-      <c r="E26" s="3">
-        <v>3300</v>
-      </c>
-      <c r="F26" s="3">
+      <c r="F26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3">
         <v>6300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>3900</v>
+      </c>
+      <c r="J26" s="3">
         <v>4700</v>
       </c>
-      <c r="I26" s="3">
-        <v>4700</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5000</v>
-      </c>
-      <c r="AB26" s="3">
-        <v>4800</v>
       </c>
       <c r="AC26" s="3">
         <v>4800</v>
       </c>
       <c r="AD26" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AE26" s="3">
         <v>4400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E27" s="3">
         <v>5800</v>
       </c>
-      <c r="E27" s="3">
-        <v>3300</v>
-      </c>
-      <c r="F27" s="3">
+      <c r="F27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3">
         <v>6300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>3900</v>
+      </c>
+      <c r="J27" s="3">
         <v>4700</v>
       </c>
-      <c r="I27" s="3">
-        <v>4700</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5000</v>
-      </c>
-      <c r="AB27" s="3">
-        <v>4800</v>
       </c>
       <c r="AC27" s="3">
         <v>4800</v>
       </c>
       <c r="AD27" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AE27" s="3">
         <v>4400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2562,17 +2623,20 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,19 +2816,22 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-300</v>
+      <c r="E32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G32" s="3">
         <v>-300</v>
@@ -2779,156 +2849,162 @@
         <v>-300</v>
       </c>
       <c r="L32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>9600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>8200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>12900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>7600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>6600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>7900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>8500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>20400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>14300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>5800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>5700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>6100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>5800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E33" s="3">
         <v>5800</v>
       </c>
-      <c r="E33" s="3">
-        <v>3300</v>
-      </c>
-      <c r="F33" s="3">
+      <c r="F33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="3">
         <v>6300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>3900</v>
+      </c>
+      <c r="J33" s="3">
         <v>4700</v>
       </c>
-      <c r="I33" s="3">
-        <v>4700</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5000</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>4800</v>
       </c>
       <c r="AC33" s="3">
         <v>4800</v>
       </c>
       <c r="AD33" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AE33" s="3">
         <v>4400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E35" s="3">
         <v>5800</v>
       </c>
-      <c r="E35" s="3">
-        <v>3300</v>
-      </c>
-      <c r="F35" s="3">
+      <c r="F35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3">
         <v>6300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>3900</v>
+      </c>
+      <c r="J35" s="3">
         <v>4700</v>
       </c>
-      <c r="I35" s="3">
-        <v>4700</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5000</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>4800</v>
       </c>
       <c r="AC35" s="3">
         <v>4800</v>
       </c>
       <c r="AD35" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AE35" s="3">
         <v>4400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="J38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
-        <v>45382</v>
-      </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,186 +3351,193 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>122100</v>
+      </c>
+      <c r="E41" s="3">
         <v>139600</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="F41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G41" s="3">
         <v>225000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>165200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
+        <v>165200</v>
+      </c>
+      <c r="J41" s="3">
         <v>246500</v>
       </c>
-      <c r="I41" s="3">
-        <v>246500</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>139600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>150500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>145100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>33500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>52600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>29800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>32800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>26300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>58400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>24500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>25500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>34500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>37400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>21200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>22900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>24600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>41600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>48400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>38300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>28000</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
+        <v>200</v>
+      </c>
+      <c r="J42" s="3">
         <v>100</v>
       </c>
-      <c r="I42" s="3">
-        <v>100</v>
-      </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>114900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>351400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>347300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>433200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>323900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>421500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>301700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>304200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>162500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>225700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>136700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>209200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>106800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>167100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>182600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>119300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>30700</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3472,12 +3565,12 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M43" s="3">
         <v>5000</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
@@ -3532,8 +3625,11 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3564,8 +3660,8 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3621,41 +3717,44 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E45" s="3">
         <v>8400</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3">
         <v>7700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7600</v>
       </c>
-      <c r="H45" s="3">
-        <v>7700</v>
-      </c>
       <c r="I45" s="3">
-        <v>7700</v>
+        <v>7600</v>
       </c>
       <c r="J45" s="3">
         <v>7700</v>
       </c>
       <c r="K45" s="3">
+        <v>7700</v>
+      </c>
+      <c r="L45" s="3">
         <v>7200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8200</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -3710,40 +3809,43 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>130900</v>
+      </c>
+      <c r="E46" s="3">
         <v>148000</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F46" s="3">
+      <c r="F46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G46" s="3">
         <v>233000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>172900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
+        <v>172900</v>
+      </c>
+      <c r="J46" s="3">
         <v>254400</v>
       </c>
-      <c r="I46" s="3">
-        <v>254400</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>147500</v>
-      </c>
-      <c r="K46" s="3">
-        <v>158400</v>
       </c>
       <c r="L46" s="3">
         <v>158400</v>
       </c>
       <c r="M46" s="3">
-        <v>0</v>
+        <v>158400</v>
       </c>
       <c r="N46" s="3">
         <v>0</v>
@@ -3799,41 +3901,44 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>334400</v>
+      </c>
+      <c r="E47" s="3">
         <v>346100</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3">
         <v>290800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>286000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
+        <v>286000</v>
+      </c>
+      <c r="J47" s="3">
         <v>321600</v>
       </c>
-      <c r="I47" s="3">
-        <v>321600</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>348000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>459200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>531500</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -3888,186 +3993,195 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>35700</v>
+      </c>
+      <c r="E48" s="3">
         <v>35800</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="F48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G48" s="3">
         <v>39700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>40100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
+        <v>40100</v>
+      </c>
+      <c r="J48" s="3">
         <v>40700</v>
       </c>
-      <c r="I48" s="3">
-        <v>40700</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>41100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>41600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>42200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>42600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>43300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>37300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>37800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>38200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>38500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>38900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>39300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>39700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>40300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>40900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>41300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>41500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>41600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>41700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>41800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>42000</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E49" s="3">
         <v>13500</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
+      <c r="F49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G49" s="3">
         <v>13700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
+        <v>13800</v>
+      </c>
+      <c r="J49" s="3">
         <v>14000</v>
       </c>
-      <c r="I49" s="3">
-        <v>14000</v>
-      </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>11200</v>
-      </c>
-      <c r="R49" s="3">
-        <v>9100</v>
       </c>
       <c r="S49" s="3">
         <v>9100</v>
       </c>
       <c r="T49" s="3">
+        <v>9100</v>
+      </c>
+      <c r="U49" s="3">
         <v>9200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9400</v>
-      </c>
-      <c r="W49" s="3">
-        <v>9500</v>
       </c>
       <c r="X49" s="3">
         <v>9500</v>
       </c>
       <c r="Y49" s="3">
+        <v>9500</v>
+      </c>
+      <c r="Z49" s="3">
         <v>9600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>9800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>10000</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,41 +4361,44 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E52" s="3">
         <v>38500</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" s="3">
         <v>37700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>38200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
+        <v>38200</v>
+      </c>
+      <c r="J52" s="3">
         <v>39000</v>
       </c>
-      <c r="I52" s="3">
-        <v>39000</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>38500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>36700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>35000</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2096400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2069000</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="F54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G54" s="3">
         <v>2014600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1895400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
+        <v>1895400</v>
+      </c>
+      <c r="J54" s="3">
         <v>1981800</v>
       </c>
-      <c r="I54" s="3">
-        <v>1981800</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1852900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1856200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1864300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1834500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2069600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1964200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1974100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1843200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1967700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1796300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1788500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1574200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1629000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1526400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1499700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1391800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1449900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1480000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1385500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1287000</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,41 +4707,42 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1741900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1721600</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="3">
         <v>1675300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1550300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>1550300</v>
+      </c>
+      <c r="J57" s="3">
         <v>1648000</v>
       </c>
-      <c r="I57" s="3">
-        <v>1648000</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1522100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1541900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1564600</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
       <c r="N57" s="3">
         <v>0</v>
       </c>
@@ -4636,15 +4767,15 @@
       <c r="U57" s="3">
         <v>0</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W57" s="3">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X57" s="3">
         <v>7800</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4657,8 +4788,8 @@
       <c r="AB57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC57" s="3">
-        <v>0</v>
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD57" s="3">
         <v>0</v>
@@ -4666,41 +4797,44 @@
       <c r="AE57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E58" s="3">
         <v>10700</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
+      <c r="F58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="3">
         <v>9700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>22900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>22900</v>
+      </c>
+      <c r="J58" s="3">
         <v>18000</v>
       </c>
-      <c r="I58" s="3">
-        <v>18000</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>34100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>25300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>15400</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4755,8 +4889,11 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4787,12 +4924,12 @@
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N59" s="3">
         <v>5900</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4808,8 +4945,8 @@
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T59" s="3">
-        <v>0</v>
+      <c r="T59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U59" s="3">
         <v>0</v>
@@ -4844,41 +4981,44 @@
       <c r="AE59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1750600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1732400</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F60" s="3">
+      <c r="F60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="3">
         <v>1685000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1573200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>1573200</v>
+      </c>
+      <c r="J60" s="3">
         <v>1666000</v>
       </c>
-      <c r="I60" s="3">
-        <v>1666000</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1556200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1567100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1580000</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -4933,8 +5073,11 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4951,26 +5094,26 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>5500</v>
       </c>
-      <c r="I61" s="3">
-        <v>5500</v>
-      </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5600</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>5800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>800</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -5022,41 +5165,44 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E62" s="3">
         <v>25900</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G62" s="3">
         <v>25800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>24400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
+        <v>24400</v>
+      </c>
+      <c r="J62" s="3">
         <v>21400</v>
       </c>
-      <c r="I62" s="3">
-        <v>21400</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>21000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>18600</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -5111,8 +5257,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1782200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1758300</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F66" s="3">
+      <c r="F66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G66" s="3">
         <v>1710800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1598900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
+        <v>1598900</v>
+      </c>
+      <c r="J66" s="3">
         <v>1692900</v>
       </c>
-      <c r="I66" s="3">
-        <v>1692900</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1569100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1589500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1604400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1584800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1827900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1721600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1737000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1599200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1728500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1558400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1559800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1346700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1403600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1302400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1271200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1163800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1226200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1345000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1253800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1160600</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>201400</v>
+      </c>
+      <c r="E72" s="3">
         <v>198400</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G72" s="3">
         <v>192800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>187700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
+        <v>187700</v>
+      </c>
+      <c r="J72" s="3">
         <v>184900</v>
       </c>
-      <c r="I72" s="3">
-        <v>184900</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>180200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>173000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>168500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>162500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>156300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>151100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>148700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>148400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>142200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>140800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>144400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>143000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>141100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>139700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>139000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>138100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>134300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>135400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>130400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>125600</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>314200</v>
+      </c>
+      <c r="E76" s="3">
         <v>310700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G76" s="3">
         <v>303800</v>
       </c>
-      <c r="F76" s="3">
-        <v>303800</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>296500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
+        <v>296500</v>
+      </c>
+      <c r="J76" s="3">
         <v>289000</v>
       </c>
-      <c r="I76" s="3">
-        <v>289000</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>283800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>266700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>259900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>249700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>241700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>242600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>237100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>244000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>239100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>237800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>228700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>227400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>225400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>224000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>228500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>228000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>223800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>135000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>131800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>126400</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="J80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
-        <v>45382</v>
-      </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E81" s="3">
         <v>5800</v>
       </c>
-      <c r="E81" s="3">
-        <v>3300</v>
-      </c>
-      <c r="F81" s="3">
+      <c r="F81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3">
         <v>6300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>3900</v>
+      </c>
+      <c r="J81" s="3">
         <v>4700</v>
       </c>
-      <c r="I81" s="3">
-        <v>4700</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5000</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>4800</v>
       </c>
       <c r="AC81" s="3">
         <v>4800</v>
       </c>
       <c r="AD81" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AE81" s="3">
         <v>4400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6621,22 +6820,22 @@
         <v>600</v>
       </c>
       <c r="G83" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="H83" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="I83" s="3">
         <v>700</v>
       </c>
       <c r="J83" s="3">
+        <v>300</v>
+      </c>
+      <c r="K83" s="3">
         <v>700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
-      </c>
-      <c r="L83" s="3">
-        <v>700</v>
       </c>
       <c r="M83" s="3">
         <v>700</v>
@@ -6675,10 +6874,10 @@
         <v>700</v>
       </c>
       <c r="Y83" s="3">
+        <v>700</v>
+      </c>
+      <c r="Z83" s="3">
         <v>1500</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>700</v>
       </c>
       <c r="AA83" s="3">
         <v>700</v>
@@ -6695,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3500</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3">
         <v>1900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>9000</v>
+      </c>
+      <c r="J89" s="3">
         <v>3300</v>
       </c>
-      <c r="I89" s="3">
-        <v>3300</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13600</v>
-      </c>
-      <c r="L89" s="3">
-        <v>2400</v>
       </c>
       <c r="M89" s="3">
         <v>2400</v>
       </c>
       <c r="N89" s="3">
+        <v>2400</v>
+      </c>
+      <c r="O89" s="3">
         <v>8000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>21400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>22800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>21500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>7800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>9400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-18400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>11000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,43 +7482,44 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1400</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O91" s="3">
         <v>-100</v>
@@ -7307,34 +7528,34 @@
         <v>-100</v>
       </c>
       <c r="Q91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-500</v>
       </c>
       <c r="AA91" s="3">
         <v>-500</v>
@@ -7343,16 +7564,19 @@
         <v>-500</v>
       </c>
       <c r="AC91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-700</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-600</v>
       </c>
       <c r="AE91" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,97 +7756,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-43600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-45700</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3">
         <v>-59300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>4700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J94" s="3">
         <v>-21000</v>
       </c>
-      <c r="I94" s="3">
-        <v>-21000</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>37200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>11200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-29100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-20000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-77000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-81100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-38400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-22300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-7700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-99400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-17700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-57500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-12600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-39300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-14900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>2600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-62600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-10100</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7683,8 +7917,8 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,97 +8250,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E100" s="3">
         <v>92300</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3">
         <v>117200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-95100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
+        <v>-95100</v>
+      </c>
+      <c r="J100" s="3">
         <v>124600</v>
       </c>
-      <c r="I100" s="3">
-        <v>124600</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-113100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-19300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>24500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-237900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>95800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-29000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>131200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-123100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>170000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>210500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-56300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>107600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>14800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>106300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-86900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-24400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>90000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>97600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-89400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>83500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-30300</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8128,8 +8377,8 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -8185,93 +8434,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E102" s="3">
         <v>43100</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>59800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-81400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>-81400</v>
+      </c>
+      <c r="J102" s="3">
         <v>106900</v>
       </c>
-      <c r="I102" s="3">
-        <v>106900</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-76900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-255600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>26800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-88700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>115600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-129400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>153600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>132600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-66200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>105300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-33300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>75300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-115200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-41300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>73300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>100300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-92000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>28100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-37400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PBFS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PBFS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
   <si>
     <t>PBFS</t>
   </si>
@@ -656,239 +656,245 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
-        <v>45473</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E8" s="3">
         <v>23200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>22900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>22000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>21200</v>
+      </c>
+      <c r="I8" s="3">
         <v>22900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>22900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>20100</v>
       </c>
-      <c r="J8" s="3">
-        <v>20100</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>18000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>12100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>13300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>28400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>14600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>14200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>13600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>13300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>13000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -982,47 +988,50 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E10" s="3">
         <v>23200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>22900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>22000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>21200</v>
+      </c>
+      <c r="I10" s="3">
         <v>22900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>22900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>20100</v>
       </c>
-      <c r="J10" s="3">
-        <v>20100</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>21500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>13900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>19100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>20800</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1077,8 +1086,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1112,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1207,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,13 +1318,16 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>2000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
@@ -1322,26 +1341,26 @@
       <c r="H14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
         <v>-6000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1397,13 +1416,16 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>600</v>
@@ -1430,13 +1452,13 @@
         <v>600</v>
       </c>
       <c r="M15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="N15" s="3">
         <v>700</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1477,8 +1499,8 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>5</v>
+      <c r="AC15" s="3">
+        <v>0</v>
       </c>
       <c r="AD15" s="3" t="s">
         <v>5</v>
@@ -1492,8 +1514,11 @@
       <c r="AG15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E17" s="3">
         <v>17400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14500</v>
-      </c>
-      <c r="F17" s="3">
-        <v>14400</v>
       </c>
       <c r="G17" s="3">
         <v>14400</v>
       </c>
       <c r="H17" s="3">
+        <v>16700</v>
+      </c>
+      <c r="I17" s="3">
         <v>14400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
+        <v>14400</v>
+      </c>
+      <c r="K17" s="3">
         <v>14800</v>
       </c>
-      <c r="J17" s="3">
-        <v>14800</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>-400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4700</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>1900</v>
       </c>
       <c r="AC17" s="3">
         <v>1900</v>
       </c>
       <c r="AD17" s="3">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="AE17" s="3">
         <v>1700</v>
       </c>
       <c r="AF17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AG17" s="3">
         <v>1600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E18" s="3">
         <v>5800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>8400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I18" s="3">
         <v>8500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>8500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>5300</v>
       </c>
-      <c r="J18" s="3">
-        <v>5300</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>17600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>14600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>9200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>9100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>9600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>8800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>9500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>23700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>12700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>12300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>11900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>11600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>11400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,8 +1781,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1764,10 +1797,10 @@
         <v>200</v>
       </c>
       <c r="G20" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H20" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I20" s="3">
         <v>300</v>
@@ -1785,162 +1818,168 @@
         <v>300</v>
       </c>
       <c r="N20" s="3">
+        <v>300</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-9500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-9400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-8200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-12900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-7600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-6600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-7100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-8500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-20400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-14300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-5800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-6100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-5800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E21" s="3">
         <v>6200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I21" s="3">
         <v>8800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>8800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>5700</v>
       </c>
-      <c r="J21" s="3">
-        <v>5700</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3200</v>
-      </c>
-      <c r="X21" s="3">
-        <v>2400</v>
       </c>
       <c r="Y21" s="3">
         <v>2400</v>
       </c>
       <c r="Z21" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AA21" s="3">
         <v>1800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>7200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>6900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>6200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>6300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1977,8 +2016,8 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2034,198 +2073,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E23" s="3">
         <v>5600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>8100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I23" s="3">
         <v>8200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>8200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>5000</v>
       </c>
-      <c r="J23" s="3">
-        <v>5000</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2400</v>
-      </c>
-      <c r="X23" s="3">
-        <v>1700</v>
       </c>
       <c r="Y23" s="3">
         <v>1700</v>
       </c>
       <c r="Z23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AA23" s="3">
         <v>1100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>6500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>6200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E24" s="3">
         <v>1300</v>
-      </c>
-      <c r="E24" s="3">
-        <v>1700</v>
       </c>
       <c r="F24" s="3">
         <v>1700</v>
       </c>
       <c r="G24" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H24" s="3">
+        <v>900</v>
+      </c>
+      <c r="I24" s="3">
         <v>1900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>1900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1100</v>
       </c>
-      <c r="J24" s="3">
-        <v>1100</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1800</v>
-      </c>
-      <c r="T24" s="3">
-        <v>400</v>
       </c>
       <c r="U24" s="3">
         <v>400</v>
       </c>
       <c r="V24" s="3">
+        <v>400</v>
+      </c>
+      <c r="W24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>300</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>200</v>
       </c>
       <c r="Z24" s="3">
         <v>200</v>
       </c>
       <c r="AA24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB24" s="3">
         <v>400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E26" s="3">
         <v>4300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I26" s="3">
         <v>6300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>6300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>3900</v>
       </c>
-      <c r="J26" s="3">
-        <v>3900</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5000</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>4800</v>
       </c>
       <c r="AE26" s="3">
         <v>4800</v>
       </c>
       <c r="AF26" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AG26" s="3">
         <v>4400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E27" s="3">
         <v>4300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I27" s="3">
         <v>6300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>6300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>3900</v>
       </c>
-      <c r="J27" s="3">
-        <v>3900</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>5000</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>4800</v>
       </c>
       <c r="AE27" s="3">
         <v>4800</v>
       </c>
       <c r="AF27" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AG27" s="3">
         <v>4400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2690,17 +2750,20 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,8 +2955,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2904,10 +2973,10 @@
         <v>-200</v>
       </c>
       <c r="G32" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="H32" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="I32" s="3">
         <v>-300</v>
@@ -2925,162 +2994,168 @@
         <v>-300</v>
       </c>
       <c r="N32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>8100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>9500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>9400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>8200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>12900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>7600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>6600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>7900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>7100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>8500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>20400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>14300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>5800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>5700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>6100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>5800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E33" s="3">
         <v>4300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I33" s="3">
         <v>6300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>6300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>3900</v>
       </c>
-      <c r="J33" s="3">
-        <v>3900</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>5000</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>4800</v>
       </c>
       <c r="AE33" s="3">
         <v>4800</v>
       </c>
       <c r="AF33" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AG33" s="3">
         <v>4400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E35" s="3">
         <v>4300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I35" s="3">
         <v>6300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>6300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>3900</v>
       </c>
-      <c r="J35" s="3">
-        <v>3900</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>5000</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>4800</v>
       </c>
       <c r="AE35" s="3">
         <v>4800</v>
       </c>
       <c r="AF35" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AG35" s="3">
         <v>4400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
-        <v>45473</v>
-      </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,198 +3524,205 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>133700</v>
+      </c>
+      <c r="E41" s="3">
         <v>228600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>122100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>139600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
+        <v>96500</v>
+      </c>
+      <c r="I41" s="3">
         <v>225000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>225000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>165200</v>
       </c>
-      <c r="J41" s="3">
-        <v>165200</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>246500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>139600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>150500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>145100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>33500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>52600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>29800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>32800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>26300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>58400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>24500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>25500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>34500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>37400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>21200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>22900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>24600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>41600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>48400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>38300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>28000</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>900</v>
+      </c>
+      <c r="E42" s="3">
         <v>500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>100</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
+        <v>100</v>
+      </c>
+      <c r="M42" s="3">
         <v>200</v>
       </c>
-      <c r="K42" s="3">
-        <v>100</v>
-      </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
+        <v>700</v>
+      </c>
+      <c r="O42" s="3">
         <v>200</v>
       </c>
-      <c r="M42" s="3">
-        <v>700</v>
-      </c>
-      <c r="N42" s="3">
-        <v>200</v>
-      </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>114900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>351400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>347300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>433200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>323900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>421500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>301700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>304200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>162500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>225700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>136700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>209200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>106800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>167100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>182600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>119300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>30700</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3664,12 +3756,12 @@
       <c r="M43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N43" s="3">
+      <c r="N43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O43" s="3">
         <v>5000</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
@@ -3724,8 +3816,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3762,8 +3857,8 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3819,47 +3914,50 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E45" s="3">
         <v>9200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I45" s="3">
         <v>7700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>7700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>7600</v>
-      </c>
-      <c r="J45" s="3">
-        <v>7600</v>
-      </c>
-      <c r="K45" s="3">
-        <v>7700</v>
       </c>
       <c r="L45" s="3">
         <v>7700</v>
       </c>
       <c r="M45" s="3">
+        <v>7700</v>
+      </c>
+      <c r="N45" s="3">
         <v>7200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8200</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -3914,46 +4012,49 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>143400</v>
+      </c>
+      <c r="E46" s="3">
         <v>238300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>130900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>148000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
+        <v>104500</v>
+      </c>
+      <c r="I46" s="3">
         <v>233000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>233000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>172900</v>
       </c>
-      <c r="J46" s="3">
-        <v>172900</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>254400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>147500</v>
-      </c>
-      <c r="M46" s="3">
-        <v>158400</v>
       </c>
       <c r="N46" s="3">
         <v>158400</v>
       </c>
       <c r="O46" s="3">
-        <v>0</v>
+        <v>158400</v>
       </c>
       <c r="P46" s="3">
         <v>0</v>
@@ -4009,47 +4110,50 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>268000</v>
+      </c>
+      <c r="E47" s="3">
         <v>302300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>334400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>346100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
+        <v>352200</v>
+      </c>
+      <c r="I47" s="3">
         <v>290800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>290800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>286000</v>
       </c>
-      <c r="J47" s="3">
-        <v>286000</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>321600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>348000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>459200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>531500</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -4104,198 +4208,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>35600</v>
+      </c>
+      <c r="E48" s="3">
         <v>35300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>35700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>35800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
+        <v>35500</v>
+      </c>
+      <c r="I48" s="3">
         <v>39700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>39700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>40100</v>
       </c>
-      <c r="J48" s="3">
-        <v>40100</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>40700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>41100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>41600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>42200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>42600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>43300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>37300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>37800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>38200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>38500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>38900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>39300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>39700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>40300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>40900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>41300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>41500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>41600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>41700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>41800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>42000</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E49" s="3">
         <v>13200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
+        <v>13600</v>
+      </c>
+      <c r="I49" s="3">
         <v>13700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>13700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>13800</v>
       </c>
-      <c r="J49" s="3">
-        <v>13800</v>
-      </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>11300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>11400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>11200</v>
-      </c>
-      <c r="T49" s="3">
-        <v>9100</v>
       </c>
       <c r="U49" s="3">
         <v>9100</v>
       </c>
       <c r="V49" s="3">
+        <v>9100</v>
+      </c>
+      <c r="W49" s="3">
         <v>9200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9400</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>9500</v>
       </c>
       <c r="Z49" s="3">
         <v>9500</v>
       </c>
       <c r="AA49" s="3">
+        <v>9500</v>
+      </c>
+      <c r="AB49" s="3">
         <v>9600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>9900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>10000</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,47 +4600,50 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>45100</v>
+      </c>
+      <c r="E52" s="3">
         <v>40200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>39200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>38500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
+        <v>39400</v>
+      </c>
+      <c r="I52" s="3">
         <v>37700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>37700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>38200</v>
       </c>
-      <c r="J52" s="3">
-        <v>38200</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>39000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>38500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>36700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>35000</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
@@ -4579,8 +4698,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2150700</v>
+      </c>
+      <c r="E54" s="3">
         <v>2243300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2096400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2069000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
+        <v>1979700</v>
+      </c>
+      <c r="I54" s="3">
         <v>2014600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2014600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1895400</v>
       </c>
-      <c r="J54" s="3">
-        <v>1895400</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1981800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1852900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1856200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1864300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1834500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2069600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1964200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1974100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1843200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1967700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1796300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1788500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1574200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1629000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1526400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1499700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1391800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1449900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1480000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1385500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1287000</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,47 +4968,48 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1739200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1895000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1741900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1721600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
+        <v>1586200</v>
+      </c>
+      <c r="I57" s="3">
         <v>1675300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1675300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1550300</v>
       </c>
-      <c r="J57" s="3">
-        <v>1550300</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1648000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1522100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1541900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1564600</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
       <c r="P57" s="3">
         <v>0</v>
       </c>
@@ -4904,15 +5034,15 @@
       <c r="W57" s="3">
         <v>0</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y57" s="3">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3">
         <v>7800</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4925,8 +5055,8 @@
       <c r="AD57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE57" s="3">
-        <v>0</v>
+      <c r="AE57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF57" s="3">
         <v>0</v>
@@ -4934,47 +5064,50 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>50600</v>
+      </c>
+      <c r="E58" s="3">
         <v>7900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>10700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
+        <v>53700</v>
+      </c>
+      <c r="I58" s="3">
         <v>9700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>9700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>22900</v>
       </c>
-      <c r="J58" s="3">
-        <v>22900</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>18000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>34100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>25300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>15400</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5029,8 +5162,11 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5067,12 +5203,12 @@
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P59" s="3">
         <v>5900</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5088,8 +5224,8 @@
       <c r="U59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V59" s="3">
-        <v>0</v>
+      <c r="V59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
@@ -5124,47 +5260,50 @@
       <c r="AG59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1789800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1902900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1750600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1732400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
+        <v>1639900</v>
+      </c>
+      <c r="I60" s="3">
         <v>1685000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1685000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1573200</v>
       </c>
-      <c r="J60" s="3">
-        <v>1573200</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1666000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1556200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1567100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1580000</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -5219,13 +5358,16 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -5237,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -5246,23 +5388,23 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>5500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5600</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>5800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>800</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -5314,47 +5456,50 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E62" s="3">
         <v>26200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>31500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>25900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
+        <v>28800</v>
+      </c>
+      <c r="I62" s="3">
         <v>25800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>25800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>24400</v>
       </c>
-      <c r="J62" s="3">
-        <v>24400</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>21400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>21000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>18600</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -5409,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1826800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1929100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1782200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1758300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
+        <v>1675200</v>
+      </c>
+      <c r="I66" s="3">
         <v>1710800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1710800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1598900</v>
       </c>
-      <c r="J66" s="3">
-        <v>1598900</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1692900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1569100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1589500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1604400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1584800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1827900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1721600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1737000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1599200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1728500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1558400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1559800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1346700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1403600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1302400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1271200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1163800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1226200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1345000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1253800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1160600</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>203000</v>
+      </c>
+      <c r="E72" s="3">
         <v>199700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>201400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>198400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
+        <v>194200</v>
+      </c>
+      <c r="I72" s="3">
         <v>192800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>192800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>187700</v>
       </c>
-      <c r="J72" s="3">
-        <v>187700</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>184900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>180200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>173000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>168500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>162500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>156300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>151100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>148700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>148400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>142200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>140800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>144400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>143000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>141100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>139700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>139000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>138100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>134300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>135400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>130400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>125600</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>314200</v>
+        <v>323900</v>
       </c>
       <c r="E76" s="3">
         <v>314200</v>
       </c>
       <c r="F76" s="3">
+        <v>314200</v>
+      </c>
+      <c r="G76" s="3">
         <v>310700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
+        <v>304600</v>
+      </c>
+      <c r="I76" s="3">
         <v>303800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>303800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>296500</v>
       </c>
-      <c r="J76" s="3">
-        <v>296500</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>289000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>283800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>266700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>259900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>249700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>241700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>242600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>237100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>244000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>239100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>237800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>228700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>227400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>225400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>224000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>228500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>228000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>223800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>135000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>131800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>126400</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
-        <v>45473</v>
-      </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E81" s="3">
         <v>4300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I81" s="3">
         <v>6300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>6300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>3900</v>
       </c>
-      <c r="J81" s="3">
-        <v>3900</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>5000</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>4800</v>
       </c>
       <c r="AE81" s="3">
         <v>4800</v>
       </c>
       <c r="AF81" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AG81" s="3">
         <v>4400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,13 +7201,14 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E83" s="3">
         <v>600</v>
@@ -7028,19 +7226,19 @@
         <v>600</v>
       </c>
       <c r="J83" s="3">
+        <v>600</v>
+      </c>
+      <c r="K83" s="3">
         <v>700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>300</v>
-      </c>
-      <c r="N83" s="3">
-        <v>700</v>
       </c>
       <c r="O83" s="3">
         <v>700</v>
@@ -7079,10 +7277,10 @@
         <v>700</v>
       </c>
       <c r="AA83" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB83" s="3">
         <v>1500</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>700</v>
       </c>
       <c r="AC83" s="3">
         <v>700</v>
@@ -7099,8 +7297,11 @@
       <c r="AG83" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E89" s="3">
         <v>3900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>14900</v>
+      </c>
+      <c r="I89" s="3">
         <v>1900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>9000</v>
       </c>
-      <c r="J89" s="3">
-        <v>9000</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>13600</v>
-      </c>
-      <c r="N89" s="3">
-        <v>2400</v>
       </c>
       <c r="O89" s="3">
         <v>2400</v>
       </c>
       <c r="P89" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Q89" s="3">
         <v>8000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>21400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>22800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>21500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>7800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>9400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-18400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>11000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>7200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,8 +7923,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7713,40 +7933,40 @@
         <v>-200</v>
       </c>
       <c r="E91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="N91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>-100</v>
@@ -7755,34 +7975,34 @@
         <v>-100</v>
       </c>
       <c r="S91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-500</v>
       </c>
       <c r="AC91" s="3">
         <v>-500</v>
@@ -7791,16 +8011,19 @@
         <v>-500</v>
       </c>
       <c r="AE91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-700</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>-600</v>
       </c>
       <c r="AG91" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-37100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-43600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-45700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>-96600</v>
+      </c>
+      <c r="I94" s="3">
         <v>-59300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-59300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>4700</v>
       </c>
-      <c r="J94" s="3">
-        <v>4700</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-21000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>37200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>11200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-29100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-20000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-77000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-81100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-38400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-22300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-7700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-99400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-17700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-57500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-12600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-39300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-14900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>2600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-62600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-10100</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8157,8 +8390,8 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -8214,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,103 +8741,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-101100</v>
+      </c>
+      <c r="E100" s="3">
         <v>139700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>21000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>92300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>-46800</v>
+      </c>
+      <c r="I100" s="3">
         <v>117200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>117200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-95100</v>
       </c>
-      <c r="J100" s="3">
-        <v>-95100</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>124600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-113100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-19300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>24500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-237900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>95800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-29000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>131200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-123100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>170000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>210500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-56300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>107600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>14800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>106300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-86900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-24400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>90000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>97600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-89400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>83500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-30300</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8632,8 +8880,8 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -8689,99 +8937,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-94900</v>
+      </c>
+      <c r="E102" s="3">
         <v>106500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-17600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>43100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>-128500</v>
+      </c>
+      <c r="I102" s="3">
         <v>59800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>59800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-81400</v>
       </c>
-      <c r="J102" s="3">
-        <v>-81400</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>106900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-76900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-255600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>26800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-88700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>115600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-129400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>153600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>132600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-66200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>105300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-33300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>75300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-115200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-41300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>73300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>100300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-92000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>28100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-37400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PBFS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PBFS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>PBFS</t>
   </si>
@@ -656,245 +656,252 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
-      </c>
-      <c r="I7" s="2">
-        <v>45565</v>
       </c>
       <c r="J7" s="2">
         <v>45565</v>
       </c>
       <c r="K7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E8" s="3">
         <v>24500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>23200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>22900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>22000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>21200</v>
-      </c>
-      <c r="I8" s="3">
-        <v>22900</v>
       </c>
       <c r="J8" s="3">
         <v>22900</v>
       </c>
       <c r="K8" s="3">
+        <v>22900</v>
+      </c>
+      <c r="L8" s="3">
         <v>20100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>18000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>12100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>10700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>13300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>28400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>14600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>14200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>13600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>13300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>13000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>12400</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,50 +998,53 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E10" s="3">
         <v>24500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>23200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>22900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>22000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>21200</v>
-      </c>
-      <c r="I10" s="3">
-        <v>22900</v>
       </c>
       <c r="J10" s="3">
         <v>22900</v>
       </c>
       <c r="K10" s="3">
+        <v>22900</v>
+      </c>
+      <c r="L10" s="3">
         <v>20100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>21500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>13900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>19100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>20800</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,17 +1338,20 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
         <v>2000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1347,23 +1367,23 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>-6000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1419,16 +1439,19 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>600</v>
+      </c>
+      <c r="E15" s="3">
         <v>100</v>
-      </c>
-      <c r="E15" s="3">
-        <v>600</v>
       </c>
       <c r="F15" s="3">
         <v>600</v>
@@ -1455,13 +1478,13 @@
         <v>600</v>
       </c>
       <c r="N15" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="O15" s="3">
         <v>700</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1502,8 +1525,8 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>5</v>
+      <c r="AD15" s="3">
+        <v>0</v>
       </c>
       <c r="AE15" s="3" t="s">
         <v>5</v>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E17" s="3">
         <v>16900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>17400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16700</v>
-      </c>
-      <c r="I17" s="3">
-        <v>14400</v>
       </c>
       <c r="J17" s="3">
         <v>14400</v>
       </c>
       <c r="K17" s="3">
+        <v>14400</v>
+      </c>
+      <c r="L17" s="3">
         <v>14800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>-400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4700</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>1900</v>
       </c>
       <c r="AD17" s="3">
         <v>1900</v>
       </c>
       <c r="AE17" s="3">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="AF17" s="3">
         <v>1700</v>
       </c>
       <c r="AG17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AH17" s="3">
         <v>1600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E18" s="3">
         <v>7600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>8400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4400</v>
-      </c>
-      <c r="I18" s="3">
-        <v>8500</v>
       </c>
       <c r="J18" s="3">
         <v>8500</v>
       </c>
       <c r="K18" s="3">
+        <v>8500</v>
+      </c>
+      <c r="L18" s="3">
         <v>5300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>17600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>14600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>12500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>10000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>9800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>9200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>9100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>9600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>8800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>9500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>23700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>12700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>12300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>11900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>11600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>11400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>10900</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1803,7 +1837,7 @@
         <v>200</v>
       </c>
       <c r="I20" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J20" s="3">
         <v>300</v>
@@ -1821,165 +1855,171 @@
         <v>300</v>
       </c>
       <c r="O20" s="3">
+        <v>300</v>
+      </c>
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-9500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-9400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-8200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-12900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-6600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-7900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-20400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-14300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-5800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-5800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E21" s="3">
         <v>7400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4800</v>
-      </c>
-      <c r="I21" s="3">
-        <v>8800</v>
       </c>
       <c r="J21" s="3">
         <v>8800</v>
       </c>
       <c r="K21" s="3">
+        <v>8800</v>
+      </c>
+      <c r="L21" s="3">
         <v>5700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>8700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3200</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>2400</v>
       </c>
       <c r="Z21" s="3">
         <v>2400</v>
       </c>
       <c r="AA21" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AB21" s="3">
         <v>1800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>7200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>6900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>6200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>6300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2019,8 +2059,8 @@
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2076,204 +2116,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E23" s="3">
         <v>5300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4200</v>
-      </c>
-      <c r="I23" s="3">
-        <v>8200</v>
       </c>
       <c r="J23" s="3">
         <v>8200</v>
       </c>
       <c r="K23" s="3">
+        <v>8200</v>
+      </c>
+      <c r="L23" s="3">
         <v>5000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>8100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2400</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>1700</v>
       </c>
       <c r="Z23" s="3">
         <v>1700</v>
       </c>
       <c r="AA23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AB23" s="3">
         <v>1100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>6500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>6200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
         <v>1600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1300</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1700</v>
       </c>
       <c r="G24" s="3">
         <v>1700</v>
       </c>
       <c r="H24" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I24" s="3">
         <v>900</v>
-      </c>
-      <c r="I24" s="3">
-        <v>1900</v>
       </c>
       <c r="J24" s="3">
         <v>1900</v>
       </c>
       <c r="K24" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L24" s="3">
         <v>1100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1800</v>
-      </c>
-      <c r="U24" s="3">
-        <v>400</v>
       </c>
       <c r="V24" s="3">
         <v>400</v>
       </c>
       <c r="W24" s="3">
+        <v>400</v>
+      </c>
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>300</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>200</v>
       </c>
       <c r="AA24" s="3">
         <v>200</v>
       </c>
       <c r="AB24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC24" s="3">
         <v>400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E26" s="3">
         <v>3700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3300</v>
-      </c>
-      <c r="I26" s="3">
-        <v>6300</v>
       </c>
       <c r="J26" s="3">
         <v>6300</v>
       </c>
       <c r="K26" s="3">
+        <v>6300</v>
+      </c>
+      <c r="L26" s="3">
         <v>3900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5000</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>4800</v>
       </c>
       <c r="AF26" s="3">
         <v>4800</v>
       </c>
       <c r="AG26" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AH26" s="3">
         <v>4400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E27" s="3">
         <v>3700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3300</v>
-      </c>
-      <c r="I27" s="3">
-        <v>6300</v>
       </c>
       <c r="J27" s="3">
         <v>6300</v>
       </c>
       <c r="K27" s="3">
+        <v>6300</v>
+      </c>
+      <c r="L27" s="3">
         <v>3900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5000</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>4800</v>
       </c>
       <c r="AF27" s="3">
         <v>4800</v>
       </c>
       <c r="AG27" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AH27" s="3">
         <v>4400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2753,17 +2814,20 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
+      <c r="AF29" s="3">
+        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2979,7 +3049,7 @@
         <v>-200</v>
       </c>
       <c r="I32" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="J32" s="3">
         <v>-300</v>
@@ -2997,165 +3067,171 @@
         <v>-300</v>
       </c>
       <c r="O32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>9500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>9400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>8200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>12900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>6600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>7900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>7100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>8500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>20400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>14300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>5800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>5700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>6100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>5800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>5500</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E33" s="3">
         <v>3700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3300</v>
-      </c>
-      <c r="I33" s="3">
-        <v>6300</v>
       </c>
       <c r="J33" s="3">
         <v>6300</v>
       </c>
       <c r="K33" s="3">
+        <v>6300</v>
+      </c>
+      <c r="L33" s="3">
         <v>3900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5000</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>4800</v>
       </c>
       <c r="AF33" s="3">
         <v>4800</v>
       </c>
       <c r="AG33" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AH33" s="3">
         <v>4400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E35" s="3">
         <v>3700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3300</v>
-      </c>
-      <c r="I35" s="3">
-        <v>6300</v>
       </c>
       <c r="J35" s="3">
         <v>6300</v>
       </c>
       <c r="K35" s="3">
+        <v>6300</v>
+      </c>
+      <c r="L35" s="3">
         <v>3900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5000</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>4800</v>
       </c>
       <c r="AF35" s="3">
         <v>4800</v>
       </c>
       <c r="AG35" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AH35" s="3">
         <v>4400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
-      </c>
-      <c r="I38" s="2">
-        <v>45565</v>
       </c>
       <c r="J38" s="2">
         <v>45565</v>
       </c>
       <c r="K38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,204 +3611,211 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>156900</v>
+      </c>
+      <c r="E41" s="3">
         <v>133700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>228600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>122100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>139600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>96500</v>
-      </c>
-      <c r="I41" s="3">
-        <v>225000</v>
       </c>
       <c r="J41" s="3">
         <v>225000</v>
       </c>
       <c r="K41" s="3">
+        <v>225000</v>
+      </c>
+      <c r="L41" s="3">
         <v>165200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>246500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>139600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>150500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>145100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>33500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>52600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>29800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>32800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>26300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>58400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>24500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>25500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>34500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>37400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>21200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>22900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>24600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>41600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>48400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>38300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>28000</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E42" s="3">
         <v>900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>100</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>400</v>
       </c>
       <c r="K42" s="3">
+        <v>400</v>
+      </c>
+      <c r="L42" s="3">
         <v>200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>114900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>351400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>347300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>433200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>323900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>421500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>301700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>304200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>162500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>225700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>136700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>209200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>106800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>167100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>182600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>119300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>30700</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH42" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3759,12 +3852,12 @@
       <c r="N43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P43" s="3">
         <v>5000</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -3819,13 +3912,16 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>5</v>
+      <c r="D44" s="3">
+        <v>100</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>5</v>
@@ -3860,8 +3956,8 @@
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3917,50 +4013,53 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E45" s="3">
         <v>8900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7900</v>
-      </c>
-      <c r="I45" s="3">
-        <v>7700</v>
       </c>
       <c r="J45" s="3">
         <v>7700</v>
       </c>
       <c r="K45" s="3">
+        <v>7700</v>
+      </c>
+      <c r="L45" s="3">
         <v>7600</v>
-      </c>
-      <c r="L45" s="3">
-        <v>7700</v>
       </c>
       <c r="M45" s="3">
         <v>7700</v>
       </c>
       <c r="N45" s="3">
+        <v>7700</v>
+      </c>
+      <c r="O45" s="3">
         <v>7200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8200</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -4015,49 +4114,52 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E46" s="3">
         <v>143400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>238300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>130900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>148000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>104500</v>
-      </c>
-      <c r="I46" s="3">
-        <v>233000</v>
       </c>
       <c r="J46" s="3">
         <v>233000</v>
       </c>
       <c r="K46" s="3">
+        <v>233000</v>
+      </c>
+      <c r="L46" s="3">
         <v>172900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>254400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>147500</v>
-      </c>
-      <c r="N46" s="3">
-        <v>158400</v>
       </c>
       <c r="O46" s="3">
         <v>158400</v>
       </c>
       <c r="P46" s="3">
-        <v>0</v>
+        <v>158400</v>
       </c>
       <c r="Q46" s="3">
         <v>0</v>
@@ -4113,50 +4215,53 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>249300</v>
+      </c>
+      <c r="E47" s="3">
         <v>268000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>302300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>334400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>346100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>352200</v>
-      </c>
-      <c r="I47" s="3">
-        <v>290800</v>
       </c>
       <c r="J47" s="3">
         <v>290800</v>
       </c>
       <c r="K47" s="3">
+        <v>290800</v>
+      </c>
+      <c r="L47" s="3">
         <v>286000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>321600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>348000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>459200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>531500</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -4211,204 +4316,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E48" s="3">
         <v>35600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>35300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>35700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>35800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>35500</v>
-      </c>
-      <c r="I48" s="3">
-        <v>39700</v>
       </c>
       <c r="J48" s="3">
         <v>39700</v>
       </c>
       <c r="K48" s="3">
+        <v>39700</v>
+      </c>
+      <c r="L48" s="3">
         <v>40100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>40700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>41100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>41600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>42200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>42600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>43300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>37300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>37800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>38200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>38500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>38900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>39300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>39700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>40300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>40900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>41300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>41500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>41600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>41700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>41800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>42000</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E49" s="3">
         <v>12300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13600</v>
-      </c>
-      <c r="I49" s="3">
-        <v>13700</v>
       </c>
       <c r="J49" s="3">
         <v>13700</v>
       </c>
       <c r="K49" s="3">
+        <v>13700</v>
+      </c>
+      <c r="L49" s="3">
         <v>13800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>11200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>11300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>11400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>11200</v>
-      </c>
-      <c r="U49" s="3">
-        <v>9100</v>
       </c>
       <c r="V49" s="3">
         <v>9100</v>
       </c>
       <c r="W49" s="3">
+        <v>9100</v>
+      </c>
+      <c r="X49" s="3">
         <v>9200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>9400</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>9500</v>
       </c>
       <c r="AA49" s="3">
         <v>9500</v>
       </c>
       <c r="AB49" s="3">
+        <v>9500</v>
+      </c>
+      <c r="AC49" s="3">
         <v>9600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>9800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>9900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>10000</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,50 +4720,53 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>47400</v>
+      </c>
+      <c r="E52" s="3">
         <v>45100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>40200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>39200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>38500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>39400</v>
-      </c>
-      <c r="I52" s="3">
-        <v>37700</v>
       </c>
       <c r="J52" s="3">
         <v>37700</v>
       </c>
       <c r="K52" s="3">
+        <v>37700</v>
+      </c>
+      <c r="L52" s="3">
         <v>38200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>39000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>38500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>36700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>35000</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2221000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2150700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2243300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2096400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2069000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1979700</v>
-      </c>
-      <c r="I54" s="3">
-        <v>2014600</v>
       </c>
       <c r="J54" s="3">
         <v>2014600</v>
       </c>
       <c r="K54" s="3">
+        <v>2014600</v>
+      </c>
+      <c r="L54" s="3">
         <v>1895400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1981800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1852900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1856200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1864300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1834500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2069600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1964200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1974100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1843200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1967700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1796300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1788500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1574200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1629000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1526400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1499700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1391800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1449900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1480000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1385500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1287000</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,50 +5099,51 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1852300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1739200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1895000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1741900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1721600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1586200</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1675300</v>
       </c>
       <c r="J57" s="3">
         <v>1675300</v>
       </c>
       <c r="K57" s="3">
+        <v>1675300</v>
+      </c>
+      <c r="L57" s="3">
         <v>1550300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1648000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1522100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1541900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1564600</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
@@ -5037,15 +5168,15 @@
       <c r="X57" s="3">
         <v>0</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z57" s="3">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA57" s="3">
         <v>7800</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>5</v>
       </c>
@@ -5058,8 +5189,8 @@
       <c r="AE57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF57" s="3">
-        <v>0</v>
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG57" s="3">
         <v>0</v>
@@ -5067,50 +5198,53 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E58" s="3">
         <v>50600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>53700</v>
-      </c>
-      <c r="I58" s="3">
-        <v>9700</v>
       </c>
       <c r="J58" s="3">
         <v>9700</v>
       </c>
       <c r="K58" s="3">
+        <v>9700</v>
+      </c>
+      <c r="L58" s="3">
         <v>22900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>18000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>34100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>25300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>15400</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -5165,8 +5299,11 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5206,12 +5343,12 @@
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q59" s="3">
         <v>5900</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5227,8 +5364,8 @@
       <c r="V59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W59" s="3">
-        <v>0</v>
+      <c r="W59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X59" s="3">
         <v>0</v>
@@ -5263,50 +5400,53 @@
       <c r="AH59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1860000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1789800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1902900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1750600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1732400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1639900</v>
-      </c>
-      <c r="I60" s="3">
-        <v>1685000</v>
       </c>
       <c r="J60" s="3">
         <v>1685000</v>
       </c>
       <c r="K60" s="3">
+        <v>1685000</v>
+      </c>
+      <c r="L60" s="3">
         <v>1573200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1666000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1556200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1567100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1580000</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -5361,17 +5501,20 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>3800</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
@@ -5379,11 +5522,11 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>5200</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -5391,23 +5534,23 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>5500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5600</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>5800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>800</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -5459,50 +5602,53 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E62" s="3">
         <v>32200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>26200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>31500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>25900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>28800</v>
-      </c>
-      <c r="I62" s="3">
-        <v>25800</v>
       </c>
       <c r="J62" s="3">
         <v>25800</v>
       </c>
       <c r="K62" s="3">
+        <v>25800</v>
+      </c>
+      <c r="L62" s="3">
         <v>24400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>21400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>21000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>18600</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1892400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1826800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1929100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1782200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1758300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1675200</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1710800</v>
       </c>
       <c r="J66" s="3">
         <v>1710800</v>
       </c>
       <c r="K66" s="3">
+        <v>1710800</v>
+      </c>
+      <c r="L66" s="3">
         <v>1598900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1692900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1569100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1589500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1604400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1584800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1827900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1721600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1737000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1599200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1728500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1558400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1559800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1346700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1403600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1302400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1271200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1163800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1226200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1345000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1253800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1160600</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>208300</v>
+      </c>
+      <c r="E72" s="3">
         <v>203000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>199700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>201400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>198400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>194200</v>
-      </c>
-      <c r="I72" s="3">
-        <v>192800</v>
       </c>
       <c r="J72" s="3">
         <v>192800</v>
       </c>
       <c r="K72" s="3">
+        <v>192800</v>
+      </c>
+      <c r="L72" s="3">
         <v>187700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>184900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>180200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>173000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>168500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>162500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>156300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>151100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>148700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>148400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>142200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>140800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>144400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>143000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>141100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>139700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>139000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>138100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>134300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>135400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>130400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>125600</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>328600</v>
+      </c>
+      <c r="E76" s="3">
         <v>323900</v>
-      </c>
-      <c r="E76" s="3">
-        <v>314200</v>
       </c>
       <c r="F76" s="3">
         <v>314200</v>
       </c>
       <c r="G76" s="3">
+        <v>314200</v>
+      </c>
+      <c r="H76" s="3">
         <v>310700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>304600</v>
-      </c>
-      <c r="I76" s="3">
-        <v>303800</v>
       </c>
       <c r="J76" s="3">
         <v>303800</v>
       </c>
       <c r="K76" s="3">
+        <v>303800</v>
+      </c>
+      <c r="L76" s="3">
         <v>296500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>289000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>283800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>266700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>259900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>249700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>241700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>242600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>237100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>244000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>239100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>237800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>228700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>227400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>225400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>224000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>228500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>228000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>223800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>135000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>131800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>126400</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
-      </c>
-      <c r="I80" s="2">
-        <v>45565</v>
       </c>
       <c r="J80" s="2">
         <v>45565</v>
       </c>
       <c r="K80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E81" s="3">
         <v>3700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3300</v>
-      </c>
-      <c r="I81" s="3">
-        <v>6300</v>
       </c>
       <c r="J81" s="3">
         <v>6300</v>
       </c>
       <c r="K81" s="3">
+        <v>6300</v>
+      </c>
+      <c r="L81" s="3">
         <v>3900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5000</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>4800</v>
       </c>
       <c r="AF81" s="3">
         <v>4800</v>
       </c>
       <c r="AG81" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AH81" s="3">
         <v>4400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4100</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,16 +7400,17 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3">
         <v>400</v>
-      </c>
-      <c r="E83" s="3">
-        <v>600</v>
       </c>
       <c r="F83" s="3">
         <v>600</v>
@@ -7229,19 +7428,19 @@
         <v>600</v>
       </c>
       <c r="K83" s="3">
+        <v>600</v>
+      </c>
+      <c r="L83" s="3">
         <v>700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>300</v>
-      </c>
-      <c r="O83" s="3">
-        <v>700</v>
       </c>
       <c r="P83" s="3">
         <v>700</v>
@@ -7280,10 +7479,10 @@
         <v>700</v>
       </c>
       <c r="AB83" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC83" s="3">
         <v>1500</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>700</v>
       </c>
       <c r="AD83" s="3">
         <v>700</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E89" s="3">
         <v>5700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>14900</v>
-      </c>
-      <c r="I89" s="3">
-        <v>1900</v>
       </c>
       <c r="J89" s="3">
         <v>1900</v>
       </c>
       <c r="K89" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L89" s="3">
         <v>9000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>13600</v>
-      </c>
-      <c r="O89" s="3">
-        <v>2400</v>
       </c>
       <c r="P89" s="3">
         <v>2400</v>
       </c>
       <c r="Q89" s="3">
+        <v>2400</v>
+      </c>
+      <c r="R89" s="3">
         <v>8000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>21400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>22800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>5400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>21500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>7800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>9400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-18400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>11000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>7200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3000</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,52 +8144,53 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200</v>
+        <v>-600</v>
       </c>
       <c r="E91" s="3">
         <v>-200</v>
       </c>
       <c r="F91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-100</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R91" s="3">
         <v>-100</v>
@@ -7978,34 +8199,34 @@
         <v>-100</v>
       </c>
       <c r="T91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1100</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-500</v>
       </c>
       <c r="AD91" s="3">
         <v>-500</v>
@@ -8014,16 +8235,19 @@
         <v>-500</v>
       </c>
       <c r="AF91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-700</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>-600</v>
       </c>
       <c r="AH91" s="3">
         <v>-600</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>-600</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-37900</v>
+      </c>
+      <c r="E94" s="3">
         <v>600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-37100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-43600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-45700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-96600</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-59300</v>
       </c>
       <c r="J94" s="3">
         <v>-59300</v>
       </c>
       <c r="K94" s="3">
+        <v>-59300</v>
+      </c>
+      <c r="L94" s="3">
         <v>4700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-21000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>37200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>11200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-29100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-77000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-81100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-38400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-22300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-99400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-17700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-57500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-12600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-39300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-14900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>2600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-62600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-10100</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8393,8 +8627,8 @@
       <c r="O96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,106 +8987,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>61400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-101100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>139700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>21000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>92300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-46800</v>
-      </c>
-      <c r="I100" s="3">
-        <v>117200</v>
       </c>
       <c r="J100" s="3">
         <v>117200</v>
       </c>
       <c r="K100" s="3">
+        <v>117200</v>
+      </c>
+      <c r="L100" s="3">
         <v>-95100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>124600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-113100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-19300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>24500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-237900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>95800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-29000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>131200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-123100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>170000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>210500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-56300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>107600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>14800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>106300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-86900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-24400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>90000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>97600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-89400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>83500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-30300</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8883,8 +9132,8 @@
       <c r="O101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-94900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>106500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>43100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-128500</v>
-      </c>
-      <c r="I102" s="3">
-        <v>59800</v>
       </c>
       <c r="J102" s="3">
         <v>59800</v>
       </c>
       <c r="K102" s="3">
+        <v>59800</v>
+      </c>
+      <c r="L102" s="3">
         <v>-81400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>106900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-76900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-255600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>26800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-88700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>115600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-129400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>153600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>132600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-66200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>105300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-33300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>75300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-115200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-41300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>73300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>100300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-92000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>28100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-37400</v>
       </c>
     </row>
